--- a/Tests/excel/module06_test_cases.xlsx
+++ b/Tests/excel/module06_test_cases.xlsx
@@ -1402,19 +1402,19 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>Tạo báo cáo mới bởi học viên thuộc nhóm thực tập đang hoạt động</t>
+          <t>Create new report boi student thuoc internship group dang hoat dong</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>Kiểm tra chức năng hiển thị nút và mở giao diện tạo báo cáo mới cho học viên thuộc nhóm thực tập đang hoạt động (On-going).</t>
+          <t>Verify functionality for display nut va mo interface create new report cho student thuoc internship group dang hoat dong (On-going).</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Student.
-Học viên thuộc nhóm thực tập có trạng thái "On-going".
-Đang ở giao diện Student Portal.</t>
+          <t>User is logged in as Student.
+Hoc vien thuoc internship group co status "On-going".
+Currently on Student Portal interface.</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
@@ -1424,15 +1424,15 @@
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>1. Truy cập vào Student Portal.
-2. Kiểm tra sự xuất hiện của nút "+ New Report".
-3. Nhấp vào nút "+ New Report".</t>
+          <t>1. Truy cap vao Student Portal.
+2. Verify su xuat hien cua nut "+ New Report".
+3. Nhap vao nut "+ New Report".</t>
         </is>
       </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
-          <t>Nút "+ New Report" hiển thị rõ ràng và có thể nhấp được.
-Giao diện tạo báo cáo thực tập mới mở ra thành công.</t>
+          <t>Nut "+ New Report" display ro rang va can click duoc.
+Interface create new internship report mo ra successfully.</t>
         </is>
       </c>
       <c r="K2" s="4" t="inlineStr"/>
@@ -1448,7 +1448,7 @@
       </c>
       <c r="N2" s="4" t="inlineStr">
         <is>
-          <t>Liên quan đến M06-F01, Rule 6.1</t>
+          <t>Related to M06-F01, Rule 6.1</t>
         </is>
       </c>
     </row>
@@ -1475,19 +1475,19 @@
       </c>
       <c r="E3" s="9" t="inlineStr">
         <is>
-          <t>Ngăn chặn tạo báo cáo mới đối với học viên thuộc nhóm thực tập đã hoàn thành</t>
+          <t>Prevent create new report for student thuoc internship group da hoan thanh</t>
         </is>
       </c>
       <c r="F3" s="9" t="inlineStr">
         <is>
-          <t>Kiểm tra hệ thống ẩn nút tạo báo cáo mới nếu học viên thuộc nhóm thực tập đã hoàn thành (Completed).</t>
+          <t>Verify system an nut create new report neu student thuoc internship group da hoan thanh (Completed).</t>
         </is>
       </c>
       <c r="G3" s="9" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Student.
-Học viên thuộc nhóm thực tập có trạng thái "Completed".
-Đang ở giao diện Student Portal.</t>
+          <t>User is logged in as Student.
+Hoc vien thuoc internship group co status "Completed".
+Currently on Student Portal interface.</t>
         </is>
       </c>
       <c r="H3" s="9" t="inlineStr">
@@ -1497,14 +1497,14 @@
       </c>
       <c r="I3" s="9" t="inlineStr">
         <is>
-          <t>1. Truy cập vào Student Portal.
-2. Quan sát sự xuất hiện của nút "+ New Report".</t>
+          <t>1. Truy cap vao Student Portal.
+2. Observe su xuat hien cua nut "+ New Report".</t>
         </is>
       </c>
       <c r="J3" s="9" t="inlineStr">
         <is>
-          <t>Nút "+ New Report" không hiển thị trên giao diện.
-Học viên không thể tạo báo cáo thực tập mới.</t>
+          <t>Nut "+ New Report" not displayed tren interface.
+Hoc vien cannot create new internship report.</t>
         </is>
       </c>
       <c r="K3" s="9" t="inlineStr"/>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="N3" s="9" t="inlineStr">
         <is>
-          <t>Liên quan đến M06-F01, Rule 6.1</t>
+          <t>Related to M06-F01, Rule 6.1</t>
         </is>
       </c>
     </row>
@@ -1547,19 +1547,19 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Ngăn chặn tạo báo cáo mới đối với học viên thuộc nhóm thực tập đã lưu trữ</t>
+          <t>Prevent create new report for student thuoc internship group da archive</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>Kiểm tra hệ thống ẩn nút tạo báo cáo mới nếu học viên thuộc nhóm thực tập đã lưu trữ (Archived).</t>
+          <t>Verify system an nut create new report neu student thuoc internship group da archive (Archived).</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Student.
-Học viên thuộc nhóm thực tập có trạng thái "Archived".
-Đang ở giao diện Student Portal.</t>
+          <t>User is logged in as Student.
+Hoc vien thuoc internship group co status "Archived".
+Currently on Student Portal interface.</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
@@ -1569,14 +1569,14 @@
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>1. Truy cập vào Student Portal.
-2. Quan sát sự xuất hiện của nút "+ New Report".</t>
+          <t>1. Truy cap vao Student Portal.
+2. Observe su xuat hien cua nut "+ New Report".</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>Nút "+ New Report" không hiển thị trên giao diện.
-Học viên không thể tạo báo cáo thực tập mới.</t>
+          <t>Nut "+ New Report" not displayed tren interface.
+Hoc vien cannot create new internship report.</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr"/>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="N4" s="4" t="inlineStr">
         <is>
-          <t>Liên quan đến M06-F01, Rule 6.1</t>
+          <t>Related to M06-F01, Rule 6.1</t>
         </is>
       </c>
     </row>
@@ -1619,18 +1619,18 @@
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>Ngăn chặn tạo báo cáo mới từ tài khoản Staff</t>
+          <t>Prevent creating new report from Staff account</t>
         </is>
       </c>
       <c r="F5" s="9" t="inlineStr">
         <is>
-          <t>Kiểm tra xem tài khoản Staff có bị giới hạn quyền không được tạo báo cáo thực tập mới hay không.</t>
+          <t>Verify whether account Staff co bi gioi han quyen khong duoc create new internship report hay khong.</t>
         </is>
       </c>
       <c r="G5" s="9" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Đang ở giao diện Quản lý Học viên hoặc Quản lý Thực tập.</t>
+          <t>User is logged in as Staff.
+Currently on Student Management or Internship Management interface.</t>
         </is>
       </c>
       <c r="H5" s="9" t="inlineStr">
@@ -1640,12 +1640,12 @@
       </c>
       <c r="I5" s="9" t="inlineStr">
         <is>
-          <t>1. Truy cập giao diện báo cáo của học viên bất kỳ hoặc kiểm tra các nút chức năng trên trang báo cáo.</t>
+          <t>1. Truy cap interface report cua student bat ky hoac kiem tra cac nut chuc nang tren trang report.</t>
         </is>
       </c>
       <c r="J5" s="9" t="inlineStr">
         <is>
-          <t>Không xuất hiện nút "+ New Report" hoặc bất kỳ tùy chọn nào cho phép Staff tạo báo cáo thực tập.</t>
+          <t>Khong xuat hien nut "+ New Report" hoac bat ky tuy select nao allows Staff create internship report.</t>
         </is>
       </c>
       <c r="K5" s="9" t="inlineStr"/>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="N5" s="9" t="inlineStr">
         <is>
-          <t>Liên quan đến User Roles (Mục 4), Staff Access (Rule 6.12)</t>
+          <t>Related to User Roles (Section 4), Staff Access (Rule 6.12)</t>
         </is>
       </c>
     </row>
@@ -1688,38 +1688,38 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Lưu báo cáo tạm thời dưới dạng Nháp (Draft)</t>
+          <t>Save temporary report as Draft</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Kiểm tra chức năng lưu nháp báo cáo với thông tin chưa đầy đủ để chỉnh sửa sau.</t>
+          <t>Verify functionality for save as draft report voi thong tin chua day du de edit sau.</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Student.
-Đang ở giao diện tạo báo cáo thực tập mới.</t>
+          <t>User is logged in as Student.
+Currently on new internship report creation interface.</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>CompanySupervisorName="Nguyễn Văn B"; StartDate="2026-07-20"; Status="Draft"</t>
+          <t>CompanySupervisorName="Nguyen Van B"; StartDate="2026-07-20"; Status="Draft"</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>1. Nhập Tên giám sát của công ty là "Nguyễn Văn B".
-2. Chọn Ngày bắt đầu là "2026-07-20" (Thứ Hai).
-3. Để trống các trường bắt buộc khác.
-4. Nhấp nút "Save as Draft" (Lưu nháp).</t>
+          <t>1. Enter Ten supervisor cua company la "Nguyen Van B".
+2. Select Start Date la "2026-07-20" (Monday).
+3. De trong cac truong bat buoc khac.
+4. Nhap nut "Save as Draft" (Save as draft).</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị thông báo lưu nháp thành công.
-Báo cáo được lưu vào danh sách với trạng thái "Draft".
-Học viên có thể mở lại để tiếp tục chỉnh sửa.</t>
+          <t>System display notification save as draft successfully.
+Bao cao duoc save vao danh sach voi status "Draft".
+Hoc vien can mo lai de tiep tuc edit.</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr"/>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
-          <t>Liên quan đến M06-F02, Rule 6.2</t>
+          <t>Related to M06-F02, Rule 6.2</t>
         </is>
       </c>
     </row>
@@ -1762,38 +1762,38 @@
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>Chỉnh sửa báo cáo nháp không giới hạn số lần</t>
+          <t>Edit draft report unlimited number of times</t>
         </is>
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>Kiểm tra xem học viên có thể chỉnh sửa và lưu lại báo cáo nháp nhiều lần trước khi nộp chính thức.</t>
+          <t>Verify whether student can edit va save lai draft report nhieu lan truoc khi submit chinh thuc.</t>
         </is>
       </c>
       <c r="G7" s="9" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Student.
-Đã có sẵn một báo cáo ở trạng thái "Draft" trong danh sách.</t>
+          <t>User is logged in as Student.
+Da co san mot report o status "Draft" trong danh sach.</t>
         </is>
       </c>
       <c r="H7" s="9" t="inlineStr">
         <is>
-          <t>ReportId="REP001"; InitialStatus="Draft"; NewSupervisorName="Trần Thị C"; Tasks=[{"TaskName": "Design Database", "Description": "Create ERD", "Result": "Completed"}]</t>
+          <t>ReportId="REP001"; InitialStatus="Draft"; NewSupervisorName="Tran Thi C"; Tasks=[{"TaskName": "Design Database", "Description": "Create ERD", "Result": "Completed"}]</t>
         </is>
       </c>
       <c r="I7" s="9" t="inlineStr">
         <is>
-          <t>1. Chọn báo cáo nháp "REP001" từ danh sách và nhấp "Edit" (Chỉnh sửa).
-2. Thay đổi Tên giám sát thành "Trần Thị C".
-3. Thêm một công việc vào bảng công việc.
-4. Nhấp nút "Save as Draft".
-5. Mở lại báo cáo đó lần nữa, sửa đổi thông tin và nhấp "Save as Draft" tiếp.</t>
+          <t>1. Select draft report "REP001" tu danh sach va click "Edit" (Edit).
+2. Thay doi Ten supervisor thanh "Tran Thi C".
+3. Add mot task vao task table.
+4. Nhap nut "Save as Draft".
+5. Mo lai report do lan nua, sua doi thong tin va click "Save as Draft" tiep.</t>
         </is>
       </c>
       <c r="J7" s="9" t="inlineStr">
         <is>
-          <t>Hệ thống cho phép chỉnh sửa và lưu thành công tất cả các thay đổi mà không giới hạn số lần.
-Trạng thái báo cáo vẫn giữ nguyên là "Draft" sau mỗi lần lưu nháp.</t>
+          <t>System allows edit va save successfully tat ca cac thay doi ma without limit times.
+Status report van giu nguyen la "Draft" sau moi lan save as draft.</t>
         </is>
       </c>
       <c r="K7" s="9" t="inlineStr"/>
@@ -1809,11 +1809,11 @@
       </c>
       <c r="N7" s="9" t="inlineStr">
         <is>
-          <t>Liên quan đến M06-F02, Rule 6.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="120" customHeight="1">
+          <t>Related to M06-F02, Rule 6.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="105" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>TC-M06-007</t>
@@ -1836,17 +1836,17 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Báo cáo nháp không gửi email và không hiển thị đối với Staff</t>
+          <t>Draft report does not send emails and is hidden from Staff</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Đảm bảo báo cáo nháp không kích hoạt tính năng gửi email và không thể nhìn thấy bởi tài khoản Staff.</t>
+          <t>Dam bao draft report khong kich hoat tinh nang gui email va cannot nhin thay boi account Staff.</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>Học viên vừa thực hiện lưu nháp một báo cáo mới.</t>
+          <t>Hoc vien vua thuc hien save as draft mot new report.</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -1856,14 +1856,14 @@
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>1. Kiểm tra hòm thư của PNV Supervisor và Company Supervisor xem có email thông báo nào được gửi đi không.
-2. Đăng nhập hệ thống bằng tài khoản Staff, truy cập trang chi tiết học viên (Student Detail) của học viên này và kiểm tra danh sách báo cáo.</t>
+          <t>1. Verify hom thu cua PNV Supervisor va Company Supervisor xem co email notification nao duoc gui di khong.
+2. Log in system bang account Staff, access trang chi tiet student (Student Detail) cua student nay va kiem tra danh sach report.</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>1. Không có email nào được gửi từ hệ thống.
-2. Tài khoản Staff không nhìn thấy báo cáo nháp này trong danh sách báo cáo của học viên.</t>
+          <t>1. Khong co email nao duoc gui tu system.
+2. Tai khoan Staff khong nhin thay draft report nay trong danh sach report cua student.</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr"/>
@@ -1879,7 +1879,7 @@
       </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
-          <t>Liên quan đến M06-F02, Rule 6.2, Rule 6.12</t>
+          <t>Related to M06-F02, Rule 6.2, Rule 6.12</t>
         </is>
       </c>
     </row>
@@ -1906,36 +1906,36 @@
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>Tự động tính toán Ngày kết thúc báo cáo khi nhập Ngày bắt đầu hợp lệ</t>
+          <t>Auto-calculate End Date when valid Start Date is entered</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>Kiểm tra chức năng tự động tính toán Ngày kết thúc (End Date) dựa trên công thức Ngày bắt đầu (Start Date) + 13 ngày.</t>
+          <t>Verify functionality for auto-calculate End Date (End Date) dua tren cong thuc Start Date (Start Date) + 13 ngay.</t>
         </is>
       </c>
       <c r="G9" s="9" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Student.
-Đang ở giao diện tạo báo cáo mới.</t>
+          <t>User is logged in as Student.
+Currently on new report creation interface.</t>
         </is>
       </c>
       <c r="H9" s="9" t="inlineStr">
         <is>
-          <t>StartDate="2026-07-20" (Thứ Hai)</t>
+          <t>StartDate="2026-07-20" (Monday)</t>
         </is>
       </c>
       <c r="I9" s="9" t="inlineStr">
         <is>
-          <t>1. Nhấp chọn trường Ngày bắt đầu và nhập/chọn ngày "2026-07-20".
-2. Kiểm tra giá trị hiển thị ở trường Ngày kết thúc.
-3. Thử nhấp đúp hoặc gõ vào trường Ngày kết thúc để chỉnh sửa.</t>
+          <t>1. Nhap select truong Start Date va enter/select ngay "2026-07-20".
+2. Verify gia tri display o truong End Date.
+3. Thu click dup hoac go vao truong End Date de edit.</t>
         </is>
       </c>
       <c r="J9" s="9" t="inlineStr">
         <is>
-          <t>Trường Ngày kết thúc tự động hiển thị ngày "2026-08-02".
-Trường Ngày kết thúc bị vô hiệu hóa (disabled/read-only) và người dùng không thể chỉnh sửa thủ công.</t>
+          <t>Truong End Date tu dong display ngay "2026-08-02".
+Truong End Date bi vo hieu hoa (disabled/read-only) va user cannot edit thu cong.</t>
         </is>
       </c>
       <c r="K9" s="9" t="inlineStr"/>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="N9" s="9" t="inlineStr">
         <is>
-          <t>Liên quan đến M06-F04, Rule 6.5</t>
+          <t>Related to M06-F04, Rule 6.5</t>
         </is>
       </c>
     </row>
@@ -1978,37 +1978,37 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Ngăn chặn nộp báo cáo nếu Ngày bắt đầu không phải là thứ Hai</t>
+          <t>Prevent submitting report if Start Date is not a Monday</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Kiểm tra hệ thống báo lỗi khi Ngày bắt đầu được chọn không rơi vào thứ Hai.</t>
+          <t>Verify system bao error khi Start Date duoc select khong roi vao thu Hai.</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Student.
-Đang ở giao diện tạo báo cáo mới.</t>
+          <t>User is logged in as Student.
+Currently on new report creation interface.</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>StartDate="2026-07-21" (Thứ Ba, không phải thứ Hai); Các trường bắt buộc khác hợp lệ</t>
+          <t>StartDate="2026-07-21" (Tuesday, not thu Hai); Other required fields valid</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>1. Nhập đầy đủ thông tin hợp lệ vào các trường bắt buộc.
-2. Thay đổi Ngày bắt đầu thành "2026-07-21" (Thứ Ba).
-3. Nhấp nút "Submit" (Nộp báo cáo).
-4. Xác nhận nộp trong hộp thoại xác nhận.</t>
+          <t>1. Enter day du thong tin hop le vao cac truong bat buoc.
+2. Thay doi Start Date thanh "2026-07-21" (Tuesday).
+3. Nhap nut "Submit" (Submit report).
+4. Xac nhan submit trong hop thoai xac nhan.</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị lỗi cảnh báo Ngày bắt đầu phải là thứ Hai (ví dụ: "Start Date must be a Monday").
-Báo cáo không được nộp và trạng thái không đổi.</t>
+          <t>System display error cphoto bao Start Date phai la thu Hai (e.g.: "Start Date must be a Monday").
+Bao cao khong duoc submit va status khong doi.</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr"/>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="N10" s="4" t="inlineStr">
         <is>
-          <t>Liên quan đến Validation Rules (Mục 7), Error Handling (Mục 8)</t>
+          <t>Related to Validation Rules (Section 7), Error Handling (Section 8)</t>
         </is>
       </c>
     </row>
@@ -2051,37 +2051,37 @@
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>Ngăn chặn nộp báo cáo nếu Ngày bắt đầu nằm ngoài thời gian thực tập</t>
+          <t>Prevent submitting report if Start Date is outside internship period</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>Kiểm tra hệ thống báo lỗi khi học viên chọn Ngày bắt đầu nằm ngoài phạm vi thời gian thực tập đã cấu hình.</t>
+          <t>Verify system bao error khi student select Start Date outside pham vi period internship da cau hinh.</t>
         </is>
       </c>
       <c r="G11" s="9" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Student.
-Thời gian thực tập của học viên được cấu hình từ "2026-07-01" đến "2026-09-30".
-Đang ở giao diện tạo báo cáo mới.</t>
+          <t>User is logged in as Student.
+Thoi gian internship cua student duoc cau hinh tu "2026-07-01" den "2026-09-30".
+Currently on new report creation interface.</t>
         </is>
       </c>
       <c r="H11" s="9" t="inlineStr">
         <is>
-          <t>StartDate="2026-06-22" (Thứ Hai, trước thời gian thực tập); Các trường bắt buộc khác hợp lệ</t>
+          <t>StartDate="2026-06-22" (Monday, truoc period internship); Other required fields valid</t>
         </is>
       </c>
       <c r="I11" s="9" t="inlineStr">
         <is>
-          <t>1. Nhập đầy đủ thông tin hợp lệ vào các trường bắt buộc.
-2. Chọn Ngày bắt đầu là "2026-06-22".
-3. Nhấp nút "Submit" và xác nhận.</t>
+          <t>1. Enter day du thong tin hop le vao cac truong bat buoc.
+2. Select Start Date la "2026-06-22".
+3. Nhap nut "Submit" va xac nhan.</t>
         </is>
       </c>
       <c r="J11" s="9" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị thông báo lỗi yêu cầu Ngày bắt đầu phải nằm trong thời gian thực tập (ví dụ: "Start Date must be within the internship period").
-Báo cáo không được nộp.</t>
+          <t>System display notification error requires Start Date phai nam trong period internship (e.g.: "Start Date must be within the internship period").
+Bao cao khong duoc submit.</t>
         </is>
       </c>
       <c r="K11" s="9" t="inlineStr"/>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="N11" s="9" t="inlineStr">
         <is>
-          <t>Liên quan đến Validation Rules (Mục 7), Error Handling (Mục 8)</t>
+          <t>Related to Validation Rules (Section 7), Error Handling (Section 8)</t>
         </is>
       </c>
     </row>
@@ -2124,41 +2124,41 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Thêm và xóa các dòng công việc trong bảng công việc động</t>
+          <t>Add and remove task rows in dynamic task table</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Kiểm tra chức năng thêm mới dòng công việc và xóa bớt dòng công việc hiện tại trong bảng công việc.</t>
+          <t>Verify functionality for add moi task row va delete bot task row hien tai trong task table.</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Student.
-Đang ở giao diện tạo hoặc chỉnh sửa báo cáo.</t>
+          <t>User is logged in as Student.
+Currently on report creation or edit interface.</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>Không có dữ liệu đặc biệt</t>
+          <t>Khong co du lieu dac biet</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>1. Nhấp nút "Add Task" (Thêm công việc).
-2. Nhập thông tin vào dòng công việc vừa tạo.
-3. Nhấp nút "Add Task" một lần nữa để tạo dòng thứ 2.
-4. Nhập thông tin cho dòng thứ 2.
-5. Nhấp nút "Remove" (Xóa) tại dòng công việc thứ nhất.</t>
+          <t>1. Nhap nut "Add Task" (Add task).
+2. Enter thong tin vao task row vua create.
+3. Nhap nut "Add Task" mot lan nua de create dong thu 2.
+4. Enter thong tin cho dong thu 2.
+5. Nhap nut "Remove" (Delete) tai task row thu nhat.</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>1. Một dòng mới xuất hiện với các ô nhập: Tên công việc, Mô tả, Kết quả.
-2. Nhập liệu bình thường.
-3. Dòng thứ 2 được tạo thêm.
-4. Nhập liệu bình thường cho dòng thứ 2.
-5. Dòng thứ nhất bị xóa khỏi bảng, chỉ còn lại dòng thứ 2.</t>
+          <t>1. Mot dong moi xuat hien voi cac o enter: Ten task, Mo ta, Ket qua.
+2. Enter lieu binh thuong.
+3. Dong thu 2 duoc create add.
+4. Enter lieu binh thuong cho dong thu 2.
+5. Dong thu nhat bi delete khoi bang, chi con lai dong thu 2.</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr"/>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t>Liên quan đến M06-F05, Rule 6.6</t>
+          <t>Related to M06-F05, Rule 6.6</t>
         </is>
       </c>
     </row>
@@ -2201,35 +2201,35 @@
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>Ngăn chặn nộp báo cáo khi danh sách công việc trống</t>
+          <t>Prevent submit report khi danh sach task trong</t>
         </is>
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>Đảm bảo hệ thống bắt buộc báo cáo phải có ít nhất một công việc mới cho phép nộp.</t>
+          <t>Dam bao system bat buoc report phai co it nhat mot task moi allows submit.</t>
         </is>
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Student.
-Đang ở giao diện tạo báo cáo mới, các trường thông tin chung đã điền đầy đủ.</t>
+          <t>User is logged in as Student.
+Dang o interface create new report, cac truong thong tin chung da dien day du.</t>
         </is>
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>TaskList=Empty; Các trường bắt buộc khác hợp lệ</t>
+          <t>TaskList=Empty; Other required fields valid</t>
         </is>
       </c>
       <c r="I13" s="9" t="inlineStr">
         <is>
-          <t>1. Xóa tất cả các dòng công việc trong bảng công việc (hoặc không thêm dòng nào).
-2. Nhấp nút "Submit" và xác nhận.</t>
+          <t>1. Delete tat ca cac task row trong task table (hoac khong add dong nao).
+2. Nhap nut "Submit" va xac nhan.</t>
         </is>
       </c>
       <c r="J13" s="9" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị thông báo lỗi yêu cầu phải nhập ít nhất một công việc (ví dụ: "At least one task is required").
-Báo cáo không được nộp.</t>
+          <t>System display notification error requires phai enter it nhat mot task (e.g.: "At least one task is required").
+Bao cao khong duoc submit.</t>
         </is>
       </c>
       <c r="K13" s="9" t="inlineStr"/>
@@ -2245,11 +2245,11 @@
       </c>
       <c r="N13" s="9" t="inlineStr">
         <is>
-          <t>Liên quan đến Validation Rules (Mục 7), Error Handling (Mục 8)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="105" customHeight="1">
+          <t>Related to Validation Rules (Section 7), Error Handling (Section 8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="90" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
           <t>TC-M06-013</t>
@@ -2272,36 +2272,36 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>Ngăn chặn nộp báo cáo khi có dòng công việc chưa hoàn thành thông tin</t>
+          <t>Prevent submit report khi co task row chua hoan thanh thong tin</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Kiểm tra hệ thống báo lỗi nếu tồn tại bất kỳ dòng công việc nào bị bỏ trống Tên, Mô tả hoặc Kết quả khi nộp.</t>
+          <t>Verify system bao error neu ton tai bat ky task row nao bi bo trong Ten, Mo ta hoac Ket qua khi submit.</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Student.
-Đang ở giao diện tạo báo cáo mới.</t>
+          <t>User is logged in as Student.
+Currently on new report creation interface.</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>TaskName="Code FE"; Description=""; Result="Done" (Để trống phần Mô tả)</t>
+          <t>TaskName="Code FE"; Description=""; Result="Done" (De trong phan Mo ta)</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>1. Nhập đầy đủ thông tin chung hợp lệ.
-2. Thêm một dòng công việc, nhập Tên công việc là "Code FE", Kết quả là "Done", bỏ trống Mô tả.
-3. Nhấp nút "Submit" và xác nhận.</t>
+          <t>1. Enter day du thong tin chung hop le.
+2. Add mot task row, enter Ten task la "Code FE", Ket qua la "Done", bo trong Mo ta.
+3. Nhap nut "Submit" va xac nhan.</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>Hệ thống báo lỗi dòng công việc không hợp lệ (ví dụ: "Task fields cannot be left blank").
-Báo cáo không được nộp.</t>
+          <t>System bao error task row khong hop le (e.g.: "Task fields cannot be left blank").
+Bao cao khong duoc submit.</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr"/>
@@ -2317,7 +2317,7 @@
       </c>
       <c r="N14" s="4" t="inlineStr">
         <is>
-          <t>Liên quan đến Rule 6.6, Validation Rules (Mục 7), Error Handling (Mục 8)</t>
+          <t>Related to Rule 6.6, Validation Rules (Section 7), Error Handling (Section 8)</t>
         </is>
       </c>
     </row>
@@ -2344,18 +2344,18 @@
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>Tự động tính toán số giờ làm việc hàng ngày và tổng số giờ làm việc</t>
+          <t>Auto-calculate so gio lam viec hang ngay va tong so gio lam viec</t>
         </is>
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>Kiểm tra chức năng tự động tính tổng số giờ làm việc theo tuần và tổng cả kỳ báo cáo khi người dùng nhập số giờ làm việc hàng ngày.</t>
+          <t>Verify functionality for tu dong tinh tong so gio lam viec theo tuan va tong ca ky report khi user enter so gio lam viec hang ngay.</t>
         </is>
       </c>
       <c r="G15" s="9" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Student.
-Đang ở giao diện tạo hoặc chỉnh sửa báo cáo.</t>
+          <t>User is logged in as Student.
+Currently on report creation or edit interface.</t>
         </is>
       </c>
       <c r="H15" s="9" t="inlineStr">
@@ -2365,18 +2365,18 @@
       </c>
       <c r="I15" s="9" t="inlineStr">
         <is>
-          <t>1. Nhập số giờ làm việc cho Tuần 1 từ thứ Hai đến chủ nhật lần lượt là: 8, 8, 8, 8, 8, 0, 0.
-2. Nhập số giờ làm việc cho Tuần 2 lần lượt là: 8, 8, 8, 8, 8, 4, 0.
-3. Quan sát tổng số giờ của Tuần 1, Tuần 2 và Tổng số giờ làm việc hiển thị trên giao diện.
-4. Thay đổi số giờ ngày thứ Bảy Tuần 2 từ 4 thành 8.</t>
+          <t>1. Enter so gio lam viec cho Tuan 1 tu thu Hai den Sunday lan luot la: 8, 8, 8, 8, 8, 0, 0.
+2. Enter so gio lam viec cho Tuan 2 lan luot la: 8, 8, 8, 8, 8, 4, 0.
+3. Observe tong so gio cua Tuan 1, Tuan 2 va Tong so gio lam viec display tren interface.
+4. Thay doi so gio ngay thu Bay Tuan 2 tu 4 thanh 8.</t>
         </is>
       </c>
       <c r="J15" s="9" t="inlineStr">
         <is>
-          <t>Tổng số giờ Tuần 1 tự động hiển thị 40.
-Tổng số giờ Tuần 2 tự động hiển thị 44.
-Tổng số giờ làm việc cả kỳ báo cáo tự động hiển thị 84.
-Khi thay đổi ngày thứ Bảy Tuần 2 thành 8, tổng Tuần 2 lập tức cập nhật thành 48 và Tổng số giờ làm việc cập nhật thành 88.</t>
+          <t>Tong so gio Tuan 1 tu dong display 40.
+Tong so gio Tuan 2 tu dong display 44.
+Tong so gio lam viec ca ky report tu dong display 84.
+Khi thay doi ngay thu Bay Tuan 2 thanh 8, tong Tuan 2 lap tuc cap nhat thanh 48 va Tong so gio lam viec cap nhat thanh 88.</t>
         </is>
       </c>
       <c r="K15" s="9" t="inlineStr"/>
@@ -2392,7 +2392,7 @@
       </c>
       <c r="N15" s="9" t="inlineStr">
         <is>
-          <t>Liên quan đến M06-F06, Rule 6.7</t>
+          <t>Related to M06-F06, Rule 6.7</t>
         </is>
       </c>
     </row>
@@ -2419,18 +2419,18 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Ngăn chặn nhập số giờ làm việc là số âm</t>
+          <t>Prevent enter so gio lam viec la so am</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Đảm bảo hệ thống không chấp nhận giá trị số giờ làm việc nhỏ hơn 0.</t>
+          <t>Dam bao system khong chap nhan gia tri so gio lam viec nho hon 0.</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Student.
-Đang ở giao diện tạo hoặc chỉnh sửa báo cáo.</t>
+          <t>User is logged in as Student.
+Currently on report creation or edit interface.</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
@@ -2440,14 +2440,14 @@
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>1. Nhập giá trị -2 vào ô nhập giờ làm việc của ngày bất kỳ.
-2. Nhấn nút "Save as Draft" hoặc "Submit".</t>
+          <t>1. Enter gia tri -2 vao o enter gio lam viec cua ngay bat ky.
+2. Nhan nut "Save as Draft" hoac "Submit".</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>Hệ thống báo lỗi số giờ không hợp lệ hoặc tự động khôi phục về 0/ngăn không cho nhập số âm.
-Báo cáo không được lưu/nộp với giá trị âm.</t>
+          <t>System bao error so gio khong hop le hoac tu dong khoi phuc ve 0/ngan khong cho enter so am.
+Bao cao khong duoc save/submit voi gia tri am.</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr"/>
@@ -2463,11 +2463,11 @@
       </c>
       <c r="N16" s="4" t="inlineStr">
         <is>
-          <t>Liên quan đến Boundary Value Testing (Mục 6.7)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="60" customHeight="1">
+          <t>Related to Boundary Value Testing (Section 6.7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="75" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
           <t>TC-M06-016</t>
@@ -2490,18 +2490,18 @@
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
-          <t>Ngăn chặn nhập số giờ làm việc vượt quá 24 giờ một ngày</t>
+          <t>Prevent enter so gio lam viec exceeding 24 gio mot ngay</t>
         </is>
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>Đảm bảo hệ thống không chấp nhận giá trị số giờ làm việc lớn hơn 24 giờ cho một ngày.</t>
+          <t>Dam bao system khong chap nhan gia tri so gio lam viec lon hon 24 gio cho mot ngay.</t>
         </is>
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Student.
-Đang ở giao diện tạo hoặc chỉnh sửa báo cáo.</t>
+          <t>User is logged in as Student.
+Currently on report creation or edit interface.</t>
         </is>
       </c>
       <c r="H17" s="9" t="inlineStr">
@@ -2511,14 +2511,14 @@
       </c>
       <c r="I17" s="9" t="inlineStr">
         <is>
-          <t>1. Nhập giá trị 25 vào ô nhập giờ làm việc của ngày bất kỳ.
-2. Nhấn nút "Save as Draft" hoặc "Submit".</t>
+          <t>1. Enter gia tri 25 vao o enter gio lam viec cua ngay bat ky.
+2. Nhan nut "Save as Draft" hoac "Submit".</t>
         </is>
       </c>
       <c r="J17" s="9" t="inlineStr">
         <is>
-          <t>Hệ thống báo lỗi số giờ không thể vượt quá 24 giờ một ngày.
-Giá trị không được chấp nhận và báo cáo không được lưu/nộp.</t>
+          <t>System bao error so gio cannot exceeding 24 gio mot ngay.
+Gia tri khong duoc chap nhan va report khong duoc save/submit.</t>
         </is>
       </c>
       <c r="K17" s="9" t="inlineStr"/>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="N17" s="9" t="inlineStr">
         <is>
-          <t>Liên quan đến Boundary Value Testing (Mục 6.7)</t>
+          <t>Related to Boundary Value Testing (Section 6.7)</t>
         </is>
       </c>
     </row>
@@ -2561,18 +2561,18 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>Ngăn chặn nhập ký tự không phải số vào ô số giờ làm việc</t>
+          <t>Prevent enter ky tu not so vao o so gio lam viec</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Đảm bảo hệ thống chỉ chấp nhận dữ liệu số trong ô nhập số giờ làm việc.</t>
+          <t>Dam bao system chi chap nhan du lieu so trong o enter so gio lam viec.</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Student.
-Đang ở giao diện tạo hoặc chỉnh sửa báo cáo.</t>
+          <t>User is logged in as Student.
+Currently on report creation or edit interface.</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
@@ -2582,13 +2582,13 @@
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>1. Nhập ký tự "abc" vào ô nhập giờ làm việc của ngày bất kỳ.
-2. Kiểm tra giá trị trong ô nhập.</t>
+          <t>1. Enter ky tu "abc" vao o enter gio lam viec cua ngay bat ky.
+2. Verify gia tri trong o enter.</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>Hệ thống tự động loại bỏ ký tự chữ hoặc hiển thị lỗi và không cho phép nhập ký tự phi số.</t>
+          <t>System tu dong loai bo ky tu chu hoac display error va khong allows enter ky tu phi so.</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr"/>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="N18" s="4" t="inlineStr">
         <is>
-          <t>Liên quan đến Boundary Value Testing (Mục 6.7)</t>
+          <t>Related to Boundary Value Testing (Section 6.7)</t>
         </is>
       </c>
     </row>
@@ -2631,37 +2631,37 @@
       </c>
       <c r="E19" s="9" t="inlineStr">
         <is>
-          <t>Nộp báo cáo thành công với đầy đủ thông tin hợp lệ</t>
+          <t>Submit report successfully voi day du thong tin hop le</t>
         </is>
       </c>
       <c r="F19" s="9" t="inlineStr">
         <is>
-          <t>Kiểm tra luồng nộp báo cáo thành công khi điền đầy đủ và đúng định dạng tất cả các thông tin bắt buộc.</t>
+          <t>Verify luong submit report successfully khi dien day du va dung format tat ca cac thong tin bat buoc.</t>
         </is>
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Student.
-Đang ở giao diện tạo báo cáo thực tập.</t>
+          <t>User is logged in as Student.
+Dang o interface create internship report.</t>
         </is>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>CompanySupervisorName="Nguyễn Văn B"; StartDate="2026-07-20"; PnvSupervisorEmail="pnv.sup@passerellesnumeriques.org"; CompanySupervisorEmail="company.sup@example.com"; TaskName="Implement Login API"; TaskDesc="Develop authentication feature"; TaskResult="Completed successfully"; Week1Hours=[8,8,8,8,8,0,0]; Week2Hours=[8,8,8,8,8,0,0]; Challenges="Gặp khó khăn khi tích hợp OAuth"; SupportNeeded="Cần mentor hỗ trợ review code"</t>
+          <t>CompanySupervisorName="Nguyen Van B"; StartDate="2026-07-20"; PnvSupervisorEmail="pnv.sup@passerellesnumeriques.org"; CompanySupervisorEmail="company.sup@example.com"; TaskName="Implement Login API"; TaskDesc="Develop authentication feature"; TaskResult="Completed successfully"; Week1Hours=[8,8,8,8,8,0,0]; Week2Hours=[8,8,8,8,8,0,0]; Challenges="Gap kho khan khi tich hop OAuth"; SupportNeeded="Can mentor ho tro review code"</t>
         </is>
       </c>
       <c r="I19" s="9" t="inlineStr">
         <is>
-          <t>1. Điền đầy đủ thông tin như trong Test Data.
-2. Nhấn nút "Submit" (Nộp báo cáo).
-3. Tại hộp thoại xác nhận "Submit Report", nhấp nút "Confirm" (Xác nhận).</t>
+          <t>1. Dien day du thong tin nhu trong Test Data.
+2. Nhan nut "Submit" (Submit report).
+3. Tai hop thoai xac nhan "Submit Report", click button "Confirm" (Xac nhan).</t>
         </is>
       </c>
       <c r="J19" s="9" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị thông báo nộp báo cáo thành công.
-Trạng thái của báo cáo chuyển sang "Submitted".
-Báo cáo chuyển sang chế độ chỉ đọc.</t>
+          <t>System display notification submit report successfully.
+Status cua report chuyen sang "Submitted".
+Bao cao chuyen sang che do chi doc.</t>
         </is>
       </c>
       <c r="K19" s="9" t="inlineStr"/>
@@ -2677,7 +2677,7 @@
       </c>
       <c r="N19" s="9" t="inlineStr">
         <is>
-          <t>Liên quan đến M06-F07, Rule 6.3</t>
+          <t>Related to M06-F07, Rule 6.3</t>
         </is>
       </c>
     </row>
@@ -2704,35 +2704,35 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>Nộp báo cáo thất bại do để trống tên người giám sát công ty</t>
+          <t>Submit report failed due to empty name nguoi supervisor company</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Kiểm tra hệ thống báo lỗi khi để trống trường Tên giám sát của công ty.</t>
+          <t>Verify system bao error khi blank truong Ten supervisor cua company.</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Student.
-Đang ở giao diện tạo báo cáo mới.</t>
+          <t>User is logged in as Student.
+Currently on new report creation interface.</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>CompanySupervisorName=""; Các trường khác đều hợp lệ</t>
+          <t>CompanySupervisorName=""; Cac truong khac deu hop le</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>1. Điền đầy đủ thông tin hợp lệ trừ trường Tên giám sát công ty để trống.
-2. Nhấp nút "Submit" và xác nhận.</t>
+          <t>1. Dien day du thong tin hop le tru truong Ten supervisor company blank.
+2. Nhap nut "Submit" va xac nhan.</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>Hệ thống báo lỗi yêu cầu nhập Tên giám sát công ty (ví dụ: "Company Supervisor Name is required").
-Báo cáo không được nộp.</t>
+          <t>System bao error requires enter Ten supervisor company (e.g.: "Company Supervisor Name is required").
+Bao cao khong duoc submit.</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr"/>
@@ -2748,11 +2748,11 @@
       </c>
       <c r="N20" s="4" t="inlineStr">
         <is>
-          <t>Liên quan đến Validation Rules (Mục 7), Error Handling (Mục 8)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="60" customHeight="1">
+          <t>Related to Validation Rules (Section 7), Error Handling (Section 8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="75" customHeight="1">
       <c r="A21" s="7" t="inlineStr">
         <is>
           <t>TC-M06-020</t>
@@ -2775,35 +2775,35 @@
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>Nộp báo cáo thất bại do để trống email người giám sát PNV</t>
+          <t>Submit report failed do blank email nguoi supervisor PNV</t>
         </is>
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>Kiểm tra hệ thống báo lỗi khi để trống trường Email giám sát PNV.</t>
+          <t>Verify system bao error khi blank truong Email supervisor PNV.</t>
         </is>
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Student.
-Đang ở giao diện tạo báo cáo mới.</t>
+          <t>User is logged in as Student.
+Currently on new report creation interface.</t>
         </is>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
-          <t>PnvSupervisorEmail=""; Các trường khác đều hợp lệ</t>
+          <t>PnvSupervisorEmail=""; Cac truong khac deu hop le</t>
         </is>
       </c>
       <c r="I21" s="9" t="inlineStr">
         <is>
-          <t>1. Điền đầy đủ thông tin hợp lệ trừ trường Email giám sát PNV để trống.
-2. Nhấp nút "Submit" và xác nhận.</t>
+          <t>1. Dien day du thong tin hop le tru truong Email supervisor PNV blank.
+2. Nhap nut "Submit" va xac nhan.</t>
         </is>
       </c>
       <c r="J21" s="9" t="inlineStr">
         <is>
-          <t>Hệ thống báo lỗi yêu cầu nhập Email giám sát PNV (ví dụ: "PNV Supervisor Email is required").
-Báo cáo không được nộp.</t>
+          <t>System bao error requires enter Email supervisor PNV (e.g.: "PNV Supervisor Email is required").
+Bao cao khong duoc submit.</t>
         </is>
       </c>
       <c r="K21" s="9" t="inlineStr"/>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="N21" s="9" t="inlineStr">
         <is>
-          <t>Liên quan đến Validation Rules (Mục 7), Error Handling (Mục 8)</t>
+          <t>Related to Validation Rules (Section 7), Error Handling (Section 8)</t>
         </is>
       </c>
     </row>
@@ -2846,35 +2846,35 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>Nộp báo cáo thất bại do email người giám sát PNV sai định dạng</t>
+          <t>Submit report failed do email nguoi supervisor PNV sai format</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Kiểm tra hệ thống báo lỗi khi nhập email giám sát PNV không đúng định dạng.</t>
+          <t>Verify system bao error khi enter email supervisor PNV khong dung format.</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Student.
-Đang ở giao diện tạo báo cáo mới.</t>
+          <t>User is logged in as Student.
+Currently on new report creation interface.</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>PnvSupervisorEmail="pnv.sup"; Các trường khác đều hợp lệ</t>
+          <t>PnvSupervisorEmail="pnv.sup"; Cac truong khac deu hop le</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>1. Điền đầy đủ thông tin hợp lệ trừ trường Email giám sát PNV nhập là "pnv.sup".
-2. Nhấp nút "Submit" và xác nhận.</t>
+          <t>1. Dien day du thong tin hop le tru truong Email supervisor PNV enter la "pnv.sup".
+2. Nhap nut "Submit" va xac nhan.</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>Hệ thống báo lỗi định dạng Email giám sát PNV không hợp lệ (ví dụ: "Invalid PNV Supervisor Email format").
-Báo cáo không được nộp.</t>
+          <t>System bao error format Email supervisor PNV khong hop le (e.g.: "Invalid PNV Supervisor Email format").
+Bao cao khong duoc submit.</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr"/>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="N22" s="4" t="inlineStr">
         <is>
-          <t>Liên quan đến Validation Rules (Mục 7), Error Handling (Mục 8)</t>
+          <t>Related to Validation Rules (Section 7), Error Handling (Section 8)</t>
         </is>
       </c>
     </row>
@@ -2917,35 +2917,35 @@
       </c>
       <c r="E23" s="9" t="inlineStr">
         <is>
-          <t>Nộp báo cáo thất bại do để trống email người giám sát công ty</t>
+          <t>Submit report failed do blank email nguoi supervisor company</t>
         </is>
       </c>
       <c r="F23" s="9" t="inlineStr">
         <is>
-          <t>Kiểm tra hệ thống báo lỗi khi để trống trường Email giám sát công ty.</t>
+          <t>Verify system bao error khi blank truong Email supervisor company.</t>
         </is>
       </c>
       <c r="G23" s="9" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Student.
-Đang ở giao diện tạo báo cáo mới.</t>
+          <t>User is logged in as Student.
+Currently on new report creation interface.</t>
         </is>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
-          <t>CompanySupervisorEmail=""; Các trường khác đều hợp lệ</t>
+          <t>CompanySupervisorEmail=""; Cac truong khac deu hop le</t>
         </is>
       </c>
       <c r="I23" s="9" t="inlineStr">
         <is>
-          <t>1. Điền đầy đủ thông tin hợp lệ trừ trường Email giám sát công ty để trống.
-2. Nhấp nút "Submit" và xác nhận.</t>
+          <t>1. Dien day du thong tin hop le tru truong Email supervisor company blank.
+2. Nhap nut "Submit" va xac nhan.</t>
         </is>
       </c>
       <c r="J23" s="9" t="inlineStr">
         <is>
-          <t>Hệ thống báo lỗi yêu cầu có ít nhất một email giám sát công ty (ví dụ: "Company Supervisor Email is required").
-Báo cáo không được nộp.</t>
+          <t>System bao error requires co it nhat mot email supervisor company (e.g.: "Company Supervisor Email is required").
+Bao cao khong duoc submit.</t>
         </is>
       </c>
       <c r="K23" s="9" t="inlineStr"/>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="N23" s="9" t="inlineStr">
         <is>
-          <t>TRÙNG LẶP. Test case này trùng lặp với yêu cầu "At least one valid email address" đã được kiểm tra. Nên được loại bỏ.</t>
+          <t>TRUNG LAP. Test case nay trung lap voi requires "At least one valid email address" da duoc kiem tra. Nen duoc loai bo.</t>
         </is>
       </c>
     </row>
@@ -2988,35 +2988,35 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>Nộp báo cáo thất bại do email người giám sát công ty sai định dạng</t>
+          <t>Submit report failed do email nguoi supervisor company sai format</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Kiểm tra hệ thống báo lỗi khi nhập email giám sát công ty không đúng định dạng email.</t>
+          <t>Verify system bao error khi enter email supervisor company khong dung format email.</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Student.
-Đang ở giao diện tạo báo cáo mới.</t>
+          <t>User is logged in as Student.
+Currently on new report creation interface.</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>CompanySupervisorEmail="company.sup@"; Các trường khác đều hợp lệ</t>
+          <t>CompanySupervisorEmail="company.sup@"; Cac truong khac deu hop le</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>1. Điền đầy đủ thông tin hợp lệ trừ trường Email giám sát công ty nhập là "company.sup@".
-2. Nhấp nút "Submit" và xác nhận.</t>
+          <t>1. Dien day du thong tin hop le tru truong Email supervisor company enter la "company.sup@".
+2. Nhap nut "Submit" va xac nhan.</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>Hệ thống báo lỗi định dạng Email giám sát công ty không hợp lệ (ví dụ: "Invalid Company Supervisor Email format").
-Báo cáo không được nộp.</t>
+          <t>System bao error format Email supervisor company khong hop le (e.g.: "Invalid Company Supervisor Email format").
+Bao cao khong duoc submit.</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr"/>
@@ -3032,7 +3032,7 @@
       </c>
       <c r="N24" s="4" t="inlineStr">
         <is>
-          <t>Liên quan đến Validation Rules (Mục 7), Error Handling (Mục 8)</t>
+          <t>Related to Validation Rules (Section 7), Error Handling (Section 8)</t>
         </is>
       </c>
     </row>
@@ -3059,35 +3059,35 @@
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
-          <t>Nộp báo cáo thất bại do để trống phần mô tả khó khăn (Challenges)</t>
+          <t>Submit report failed do blank phan mo ta kho khan (Challenges)</t>
         </is>
       </c>
       <c r="F25" s="9" t="inlineStr">
         <is>
-          <t>Kiểm tra hệ thống báo lỗi khi trường Khó khăn gặp phải (Challenges) bị bỏ trống khi nộp.</t>
+          <t>Verify system bao error khi truong Kho khan gap phai (Challenges) bi bo trong khi submit.</t>
         </is>
       </c>
       <c r="G25" s="9" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Student.
-Đang ở giao diện tạo báo cáo mới.</t>
+          <t>User is logged in as Student.
+Currently on new report creation interface.</t>
         </is>
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
-          <t>Challenges=""; Các trường khác đều hợp lệ</t>
+          <t>Challenges=""; Cac truong khac deu hop le</t>
         </is>
       </c>
       <c r="I25" s="9" t="inlineStr">
         <is>
-          <t>1. Điền đầy đủ thông tin hợp lệ trừ trường Khó khăn để trống.
-2. Nhấp nút "Submit" và xác nhận.</t>
+          <t>1. Dien day du thong tin hop le tru truong Kho khan blank.
+2. Nhap nut "Submit" va xac nhan.</t>
         </is>
       </c>
       <c r="J25" s="9" t="inlineStr">
         <is>
-          <t>Hệ thống báo lỗi yêu cầu nhập Khó khăn gặp phải (ví dụ: "Challenges field is required").
-Báo cáo không được nộp.</t>
+          <t>System bao error requires enter Kho khan gap phai (e.g.: "Challenges field is required").
+Bao cao khong duoc submit.</t>
         </is>
       </c>
       <c r="K25" s="9" t="inlineStr"/>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="N25" s="9" t="inlineStr">
         <is>
-          <t>Liên quan đến Validation Rules (Mục 7), Error Handling (Mục 8)</t>
+          <t>Related to Validation Rules (Section 7), Error Handling (Section 8)</t>
         </is>
       </c>
     </row>
@@ -3130,35 +3130,35 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>Nộp báo cáo thất bại do để trống phần hỗ trợ cần thiết (Support Needed)</t>
+          <t>Submit report failed do blank phan ho tro can thiet (Support Needed)</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Kiểm tra hệ thống báo lỗi khi trường Hỗ trợ cần thiết (Support Needed) bị bỏ trống khi nộp.</t>
+          <t>Verify system bao error khi truong Ho tro can thiet (Support Needed) bi bo trong khi submit.</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Student.
-Đang ở giao diện tạo báo cáo mới.</t>
+          <t>User is logged in as Student.
+Currently on new report creation interface.</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>SupportNeeded=""; Các trường khác đều hợp lệ</t>
+          <t>SupportNeeded=""; Cac truong khac deu hop le</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>1. Điền đầy đủ thông tin hợp lệ trừ trường Hỗ trợ cần thiết để trống.
-2. Nhấp nút "Submit" và xác nhận.</t>
+          <t>1. Dien day du thong tin hop le tru truong Ho tro can thiet blank.
+2. Nhap nut "Submit" va xac nhan.</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>Hệ thống báo lỗi yêu cầu nhập Hỗ trợ cần thiết (ví dụ: "Support Needed field is required").
-Báo cáo không được nộp.</t>
+          <t>System bao error requires enter Ho tro can thiet (e.g.: "Support Needed field is required").
+Bao cao khong duoc submit.</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr"/>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="N26" s="4" t="inlineStr">
         <is>
-          <t>Liên quan đến Validation Rules (Mục 7), Error Handling (Mục 8)</t>
+          <t>Related to Validation Rules (Section 7), Error Handling (Section 8)</t>
         </is>
       </c>
     </row>
@@ -3201,36 +3201,36 @@
       </c>
       <c r="E27" s="9" t="inlineStr">
         <is>
-          <t>Hủy xác nhận nộp báo cáo</t>
+          <t>Huy xac nhan submit report</t>
         </is>
       </c>
       <c r="F27" s="9" t="inlineStr">
         <is>
-          <t>Đảm bảo hệ thống không nộp báo cáo nếu người dùng nhấp nút Hủy (Cancel) trên hộp thoại xác nhận nộp.</t>
+          <t>Dam bao system khong submit report neu user click button Huy (Cancel) tren hop thoai xac nhan submit.</t>
         </is>
       </c>
       <c r="G27" s="9" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Student.
-Đang ở giao diện tạo báo cáo và đã nhập đầy đủ thông tin hợp lệ.</t>
+          <t>User is logged in as Student.
+Dang o interface create report va da enter day du thong tin hop le.</t>
         </is>
       </c>
       <c r="H27" s="9" t="inlineStr">
         <is>
-          <t>Các thông tin hợp lệ</t>
+          <t>Cac thong tin hop le</t>
         </is>
       </c>
       <c r="I27" s="9" t="inlineStr">
         <is>
-          <t>1. Nhấp nút "Submit".
-2. Khi hộp thoại xác nhận "Submit Report" hiện lên, nhấp nút "Cancel" (Hủy) hoặc nút đóng hộp thoại.</t>
+          <t>1. Nhap nut "Submit".
+2. Khi hop thoai xac nhan "Submit Report" hien len, click button "Cancel" (Huy) hoac nut dong hop thoai.</t>
         </is>
       </c>
       <c r="J27" s="9" t="inlineStr">
         <is>
-          <t>Hộp thoại đóng lại.
-Báo cáo không được nộp và trạng thái vẫn là nháp hoặc chưa lưu.
-Người dùng vẫn có thể tiếp tục chỉnh sửa báo cáo.</t>
+          <t>Hop thoai dong lai.
+Bao cao khong duoc submit va status van la draft hoac chua save.
+Nguoi dung van can tiep tuc edit report.</t>
         </is>
       </c>
       <c r="K27" s="9" t="inlineStr"/>
@@ -3246,7 +3246,7 @@
       </c>
       <c r="N27" s="9" t="inlineStr">
         <is>
-          <t>Liên quan đến Rule 6.3, Workflow</t>
+          <t>Related to Rule 6.3, Workflow</t>
         </is>
       </c>
     </row>
@@ -3273,18 +3273,18 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>Báo cáo đã nộp chuyển sang trạng thái chỉ đọc mãi mãi</t>
+          <t>Bao cao da submit chuyen sang status chi doc mai mai</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Đảm bảo báo cáo sau khi nộp (Submitted) sẽ bị khóa, không thể chỉnh sửa hay xóa bởi học viên.</t>
+          <t>Dam bao report sau khi submit (Submitted) se bi khoa, cannot edit hay delete boi student.</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Student.
-Có một báo cáo trong danh sách đã ở trạng thái "Submitted".</t>
+          <t>User is logged in as Student.
+Co mot report trong danh sach da o status "Submitted".</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
@@ -3294,16 +3294,16 @@
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>1. Mở xem chi tiết báo cáo đã nộp.
-2. Kiểm tra sự xuất hiện của nút "Edit" (Chỉnh sửa), "Save" (Lưu), hoặc "Delete" (Xóa).
-3. Thử nhấp đúp hoặc thay đổi nội dung các trường thông tin.</t>
+          <t>1. Mo xem chi tiet report da submit.
+2. Verify su xuat hien cua nut "Edit" (Edit), "Save" (Save), hoac "Delete" (Delete).
+3. Thu click dup hoac thay doi noi dung cac truong thong tin.</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>Nút "Edit" và "Save as Draft" không hiển thị.
-Tất cả các trường thông tin đều ở trạng thái chỉ đọc (disabled/read-only).
-Học viên không thể sửa đổi bất kỳ dữ liệu nào.</t>
+          <t>Nut "Edit" va "Save as Draft" not displayed.
+Tat ca cac truong thong tin deu o status chi doc (disabled/read-only).
+Hoc vien cannot sua doi bat ky du lieu nao.</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr"/>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="N28" s="4" t="inlineStr">
         <is>
-          <t>Liên quan đến M06-F07, Rule 6.3, Rule 6.11</t>
+          <t>Related to M06-F07, Rule 6.3, Rule 6.11</t>
         </is>
       </c>
     </row>
@@ -3346,38 +3346,38 @@
       </c>
       <c r="E29" s="9" t="inlineStr">
         <is>
-          <t>Gửi email thông báo tự động khi nộp báo cáo thành công</t>
+          <t>Gui email notification tu dong khi submit report successfully</t>
         </is>
       </c>
       <c r="F29" s="9" t="inlineStr">
         <is>
-          <t>Kiểm tra xem hệ thống có tự động gửi email với đúng định dạng và đúng đối tượng sau khi nộp báo cáo hay không.</t>
+          <t>Verify whether system co tu dong gui email voi dung format va dung doi tuong sau khi submit report hay khong.</t>
         </is>
       </c>
       <c r="G29" s="9" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Student tên "Nguyễn Văn A", lớp "PNV26A", làm việc tại công ty "TechCorp".
-Hệ thống kết nối email hoạt động bình thường.</t>
+          <t>Nguoi dung da log in voi quyen Student ten "Nguyen Van A", lop "PNV26A", lam viec tai company "TechCorp".
+System ket noi email hoat dong binh thuong.</t>
         </is>
       </c>
       <c r="H29" s="9" t="inlineStr">
         <is>
-          <t>StudentName="Nguyễn Văn A"; BatchName="PNV26A"; Company="TechCorp"; PnvSupervisorEmail="pnv.sup@passerellesnumeriques.org"; CompanySupervisorEmail="company.sup@example.com"; StudentEmail="student01@student.passerellesnumeriques.org"; StartDate="2026-07-20"; EndDate="2026-08-02"</t>
+          <t>StudentName="Nguyen Van A"; BatchName="PNV26A"; Company="TechCorp"; PnvSupervisorEmail="pnv.sup@passerellesnumeriques.org"; CompanySupervisorEmail="company.sup@example.com"; StudentEmail="student01@student.passerellesnumeriques.org"; StartDate="2026-07-20"; EndDate="2026-08-02"</t>
         </is>
       </c>
       <c r="I29" s="9" t="inlineStr">
         <is>
-          <t>1. Điền đầy đủ thông tin báo cáo của học viên "Nguyễn Văn A" làm việc tại "TechCorp" từ ngày "2026-07-20" đến "2026-08-02".
-2. Nhấp nút "Submit" và xác nhận nộp báo cáo.
-3. Kiểm tra email nhận được từ tài khoản PNV Supervisor, Company Supervisor và học viên.</t>
+          <t>1. Dien day du thong tin report cua student "Nguyen Van A" lam viec tai "TechCorp" tu ngay "2026-07-20" den "2026-08-02".
+2. Nhap nut "Submit" va xac nhan submit report.
+3. Verify email nhan duoc tu account PNV Supervisor, Company Supervisor va student.</t>
         </is>
       </c>
       <c r="J29" s="9" t="inlineStr">
         <is>
-          <t>1. Báo cáo nộp thành công.
-2. Email được tự động gửi đến địa chỉ "pnv.sup@passerellesnumeriques.org" và "company.sup@example.com".
-3. Email được gửi CC cho "student01@student.passerellesnumeriques.org" và "ero.vietnam@passerellesnumeriques.org".
-4. Tiêu đề email có định dạng chính xác: "[PNV26A] [Bi-Weekly Internship Report] Nguyễn Văn A - TechCorp (Period: 20/07 – 02/08)"</t>
+          <t>1. Bao cao submit successfully.
+2. Email duoc tu dong gui den dia chi "pnv.sup@passerellesnumeriques.org" va "company.sup@example.com".
+3. Email duoc gui CC cho "student01@student.passerellesnumeriques.org" va "ero.vietnam@passerellesnumeriques.org".
+4. Tieu de email co format chinh xac: "[PNV26A] [Bi-Weekly Internship Report] Nguyen Van A - TechCorp (Period: 20/07 – 02/08)"</t>
         </is>
       </c>
       <c r="K29" s="9" t="inlineStr"/>
@@ -3393,7 +3393,7 @@
       </c>
       <c r="N29" s="9" t="inlineStr">
         <is>
-          <t>Liên quan đến M06-F08, Rule 6.10</t>
+          <t>Related to M06-F08, Rule 6.10</t>
         </is>
       </c>
     </row>
@@ -3420,36 +3420,36 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>Xử lý lỗi khi gửi email thông báo thất bại</t>
+          <t>Xu ly error khi gui email notification failed</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>Đảm bảo hệ thống vẫn ghi nhận nộp báo cáo thành công và hiển thị cảnh báo nếu quá trình gửi email tự động bị lỗi.</t>
+          <t>Dam bao system van ghi nhan submit report successfully va display cphoto bao neu qua trinh gui email tu dong bi error.</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Student.
-Hệ thống email bị lỗi kết nối hoặc tài khoản gửi bị chặn.</t>
+          <t>User is logged in as Student.
+System email bi error ket noi hoac account gui bi chan.</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>Các thông tin hợp lệ</t>
+          <t>Cac thong tin hop le</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>1. Điền đầy đủ thông tin báo cáo hợp lệ.
-2. Nhấp nút "Submit" và xác nhận nộp báo cáo.</t>
+          <t>1. Dien day du thong tin report hop le.
+2. Nhap nut "Submit" va xac nhan submit report.</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>Hệ thống hiển thị cảnh báo lỗi gửi email (ví dụ: "Email notification failed: [Reason]").
-Báo cáo vẫn được nộp thành công và trạng thái chuyển sang "Submitted" bình thường.
-Dữ liệu báo cáo bị khóa thành chỉ đọc.</t>
+          <t>System display cphoto bao error gui email (e.g.: "Email notification failed: [Reason]").
+Bao cao van duoc submit successfully va status chuyen sang "Submitted" binh thuong.
+Du lieu report bi khoa thanh chi doc.</t>
         </is>
       </c>
       <c r="K30" s="4" t="inlineStr"/>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="N30" s="4" t="inlineStr">
         <is>
-          <t>Liên quan đến Rule 6.11, Error Handling (Mục 8)</t>
+          <t>Related to Rule 6.11, Error Handling (Section 8)</t>
         </is>
       </c>
     </row>
@@ -3492,37 +3492,37 @@
       </c>
       <c r="E31" s="9" t="inlineStr">
         <is>
-          <t>Staff xem báo cáo thực tập của học viên</t>
+          <t>Staff xem internship report cua student</t>
         </is>
       </c>
       <c r="F31" s="9" t="inlineStr">
         <is>
-          <t>Kiểm tra xem tài khoản Staff có thể xem được nội dung chi tiết báo cáo đã nộp của học viên hay không.</t>
+          <t>Verify whether account Staff can xem duoc noi dung chi tiet report da submit cua student hay khong.</t>
         </is>
       </c>
       <c r="G31" s="9" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Học viên "Nguyễn Văn A" đã nộp báo cáo thực tập.</t>
+          <t>User is logged in as Staff.
+Hoc vien "Nguyen Van A" da submit internship report.</t>
         </is>
       </c>
       <c r="H31" s="9" t="inlineStr">
         <is>
-          <t>StudentName="Nguyễn Văn A"; ReportStatus="Submitted"</t>
+          <t>StudentName="Nguyen Van A"; ReportStatus="Submitted"</t>
         </is>
       </c>
       <c r="I31" s="9" t="inlineStr">
         <is>
-          <t>1. Đăng nhập với quyền Staff.
-2. Truy cập vào trang chi tiết học viên "Nguyễn Văn A".
-3. Tìm phần Báo cáo thực tập của học viên.
-4. Nhấp vào xem chi tiết báo cáo đã nộp.</t>
+          <t>1. Log in voi quyen Staff.
+2. Truy cap vao trang chi tiet student "Nguyen Van A".
+3. Tim phan Bao cao internship cua student.
+4. Nhap vao xem chi tiet report da submit.</t>
         </is>
       </c>
       <c r="J31" s="9" t="inlineStr">
         <is>
-          <t>Staff có thể xem đầy đủ nội dung chi tiết của báo cáo học viên đã nộp.
-Báo cáo hiển thị chính xác các thông tin học viên đã điền.</t>
+          <t>Staff can xem day du noi dung chi tiet cua report student da submit.
+Bao cao display chinh xac cac thong tin student da dien.</t>
         </is>
       </c>
       <c r="K31" s="9" t="inlineStr"/>
@@ -3538,7 +3538,7 @@
       </c>
       <c r="N31" s="9" t="inlineStr">
         <is>
-          <t>Liên quan đến M06-F09, Rule 6.12</t>
+          <t>Related to M06-F09, Rule 6.12</t>
         </is>
       </c>
     </row>
@@ -3565,35 +3565,35 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>Staff không thể sửa hoặc xóa báo cáo của học viên</t>
+          <t>Staff cannot sua hoac delete report cua student</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>Đảm bảo Staff chỉ có quyền xem (Read-only) và không thể thay đổi thông tin hoặc xóa báo cáo của học viên.</t>
+          <t>Dam bao Staff chi co quyen xem (Read-only) va cannot thay doi thong tin hoac delete report cua student.</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>Người dùng đã đăng nhập với quyền Staff.
-Đang ở màn hình xem chi tiết báo cáo của học viên "Nguyễn Văn A".</t>
+          <t>User is logged in as Staff.
+Dang o man hinh xem chi tiet report cua student "Nguyen Van A".</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>StudentName="Nguyễn Văn A"</t>
+          <t>StudentName="Nguyen Van A"</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>1. Kiểm tra sự xuất hiện của các nút chỉnh sửa (Edit), lưu (Save), hoặc xóa (Delete) báo cáo.
-2. Thử thay đổi giá trị trong các trường thông tin của báo cáo học viên.</t>
+          <t>1. Verify su xuat hien cua cac nut edit (Edit), save (Save), hoac delete (Delete) report.
+2. Thu thay doi gia tri trong cac truong thong tin cua report student.</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>Không có bất kỳ nút hoặc tuỳ chọn chỉnh sửa/xóa nào hiển thị với tài khoản Staff.
-Tất cả các trường thông tin đều bị khóa, không thể tương tác thay đổi giá trị.</t>
+          <t>Khong co bat ky nut hoac tuy select edit/delete nao display voi account Staff.
+Tat ca cac truong thong tin deu bi khoa, cannot tuong tac thay doi gia tri.</t>
         </is>
       </c>
       <c r="K32" s="4" t="inlineStr"/>
@@ -3609,7 +3609,7 @@
       </c>
       <c r="N32" s="4" t="inlineStr">
         <is>
-          <t>Liên quan đến Staff Access (Rule 6.12)</t>
+          <t>Related to Staff Access (Rule 6.12)</t>
         </is>
       </c>
     </row>

--- a/Tests/excel/module06_test_cases.xlsx
+++ b/Tests/excel/module06_test_cases.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Module06" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Report" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Module06" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Module06'!$A$1:$N$32</definedName>
@@ -398,14 +398,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -429,10 +429,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="FF0000"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -456,10 +456,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="FFFF00"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -483,10 +483,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="00FF00"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -515,8 +515,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -542,8 +542,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -569,7 +569,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>7</col>
@@ -584,9 +584,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1028,12 +1028,12 @@
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="28" t="inlineStr">
         <is>
-          <t>M06-F03</t>
+          <t>M06-F02</t>
         </is>
       </c>
       <c r="B10" s="29" t="inlineStr">
         <is>
-          <t>Submission Validation</t>
+          <t>Draft Saving &amp; Editing</t>
         </is>
       </c>
       <c r="C10" s="30">
@@ -1056,12 +1056,12 @@
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="22" t="inlineStr">
         <is>
-          <t>M06-F02</t>
+          <t>M06-F03</t>
         </is>
       </c>
       <c r="B11" s="23" t="inlineStr">
         <is>
-          <t>Draft Saving</t>
+          <t>Automatic Date Calculation</t>
         </is>
       </c>
       <c r="C11" s="24">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="B12" s="29" t="inlineStr">
         <is>
-          <t>Auto-calculated End Date</t>
+          <t>Dynamic Task Table Management</t>
         </is>
       </c>
       <c r="C12" s="30">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="B13" s="23" t="inlineStr">
         <is>
-          <t>Dynamic Task Table</t>
+          <t>Working Hours Calculation</t>
         </is>
       </c>
       <c r="C13" s="24">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="B14" s="29" t="inlineStr">
         <is>
-          <t>Auto-calculated Total Hours</t>
+          <t>Report Submission</t>
         </is>
       </c>
       <c r="C14" s="30">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="B15" s="23" t="inlineStr">
         <is>
-          <t>Report Submission</t>
+          <t>Read-only Submitted Reports</t>
         </is>
       </c>
       <c r="C15" s="24">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="B16" s="29" t="inlineStr">
         <is>
-          <t>Automatic Email Notification</t>
+          <t>Automated Email Notifications</t>
         </is>
       </c>
       <c r="C16" s="30">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="B17" s="23" t="inlineStr">
         <is>
-          <t>Staff View of Student Reports</t>
+          <t>Staff Report Viewing</t>
         </is>
       </c>
       <c r="C17" s="24">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Module 06 – Bi-Weekly Internship Reports</t>
+          <t>Module 06 - Bi-Weekly Internship Reports</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -1402,37 +1402,37 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>Create new report boi student thuoc internship group dang hoat dong</t>
+          <t>Create New Report by Student in Active Internship Group</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>Verify functionality for display nut va mo interface create new report cho student thuoc internship group dang hoat dong (On-going).</t>
+          <t>Verify button visibility and interface opening for creating a new report when student belongs to an active (On-going) internship group.</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
           <t>User is logged in as Student.
-Hoc vien thuoc internship group co status "On-going".
+Student belongs to an internship group with status "On-going".
 Currently on Student Portal interface.</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>BatchName="PNV26A"; GroupStatus="On-going"</t>
+          <t>StudentEmail="student1@student.passerellesnumeriques.org"; GroupStatus="On-going"</t>
         </is>
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>1. Truy cap vao Student Portal.
-2. Verify su xuat hien cua nut "+ New Report".
-3. Nhap vao nut "+ New Report".</t>
+          <t>1. Access Student Portal;
+2. Click Create Internship Report button;
+3. Observe interface.</t>
         </is>
       </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
-          <t>Nut "+ New Report" display ro rang va can click duoc.
-Interface create new internship report mo ra successfully.</t>
+          <t>Create Internship Report button is displayed and clickable.
+System opens report submission interface with auto-filled student profile info.</t>
         </is>
       </c>
       <c r="K2" s="4" t="inlineStr"/>
@@ -1448,7 +1448,7 @@
       </c>
       <c r="N2" s="4" t="inlineStr">
         <is>
-          <t>Related to M06-F01, Rule 6.1</t>
+          <t>Related Requirement: M06-F01, Business Rules 6.1</t>
         </is>
       </c>
     </row>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>Module 06 – Bi-Weekly Internship Reports</t>
+          <t>Module 06 - Bi-Weekly Internship Reports</t>
         </is>
       </c>
       <c r="C3" s="8" t="inlineStr">
@@ -1475,36 +1475,36 @@
       </c>
       <c r="E3" s="9" t="inlineStr">
         <is>
-          <t>Prevent create new report for student thuoc internship group da hoan thanh</t>
+          <t>Prevent Creating New Report for Student in Completed Internship Group</t>
         </is>
       </c>
       <c r="F3" s="9" t="inlineStr">
         <is>
-          <t>Verify system an nut create new report neu student thuoc internship group da hoan thanh (Completed).</t>
+          <t>Verify system hides Create Internship Report button if student belongs to a completed internship group.</t>
         </is>
       </c>
       <c r="G3" s="9" t="inlineStr">
         <is>
           <t>User is logged in as Student.
-Hoc vien thuoc internship group co status "Completed".
+Student belongs to an internship group with status "Completed".
 Currently on Student Portal interface.</t>
         </is>
       </c>
       <c r="H3" s="9" t="inlineStr">
         <is>
-          <t>BatchName="PNV26A"; GroupStatus="Completed"</t>
+          <t>StudentEmail="student2@student.passerellesnumeriques.org"; GroupStatus="Completed"</t>
         </is>
       </c>
       <c r="I3" s="9" t="inlineStr">
         <is>
-          <t>1. Truy cap vao Student Portal.
-2. Observe su xuat hien cua nut "+ New Report".</t>
+          <t>1. Access Student Portal;
+2. Observe interface.</t>
         </is>
       </c>
       <c r="J3" s="9" t="inlineStr">
         <is>
-          <t>Nut "+ New Report" not displayed tren interface.
-Hoc vien cannot create new internship report.</t>
+          <t>Create Internship Report button is hidden or disabled.
+Student cannot open report creation interface.</t>
         </is>
       </c>
       <c r="K3" s="9" t="inlineStr"/>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="N3" s="9" t="inlineStr">
         <is>
-          <t>Related to M06-F01, Rule 6.1</t>
+          <t>Related Requirement: M06-F01, Business Rules 6.1</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Module 06 – Bi-Weekly Internship Reports</t>
+          <t>Module 06 - Bi-Weekly Internship Reports</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -1547,36 +1547,36 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Prevent create new report for student thuoc internship group da archive</t>
+          <t>Prevent Creating New Report for Student in Archived Internship Group</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>Verify system an nut create new report neu student thuoc internship group da archive (Archived).</t>
+          <t>Verify system hides Create Internship Report button if student belongs to an archived internship group.</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
           <t>User is logged in as Student.
-Hoc vien thuoc internship group co status "Archived".
+Student belongs to an internship group with status "Archived".
 Currently on Student Portal interface.</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>BatchName="PNV26A"; GroupStatus="Archived"</t>
+          <t>StudentEmail="student3@student.passerellesnumeriques.org"; GroupStatus="Archived"</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>1. Truy cap vao Student Portal.
-2. Observe su xuat hien cua nut "+ New Report".</t>
+          <t>1. Access Student Portal;
+2. Observe interface.</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>Nut "+ New Report" not displayed tren interface.
-Hoc vien cannot create new internship report.</t>
+          <t>Create Internship Report button is hidden or disabled.
+Student cannot open report creation interface.</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr"/>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="N4" s="4" t="inlineStr">
         <is>
-          <t>Related to M06-F01, Rule 6.1</t>
+          <t>Related Requirement: M06-F01, Business Rules 6.1</t>
         </is>
       </c>
     </row>
@@ -1604,48 +1604,49 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Module 06 – Bi-Weekly Internship Reports</t>
+          <t>Module 06 - Bi-Weekly Internship Reports</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>M06-F03</t>
+          <t>M06-F01</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>Submission Validation</t>
+          <t>Report Creation</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>Prevent creating new report from Staff account</t>
+          <t>Prevent Creating New Report from Staff Account</t>
         </is>
       </c>
       <c r="F5" s="9" t="inlineStr">
         <is>
-          <t>Verify whether account Staff co bi gioi han quyen khong duoc create new internship report hay khong.</t>
+          <t>Verify system hides report creation feature from Staff role.</t>
         </is>
       </c>
       <c r="G5" s="9" t="inlineStr">
         <is>
           <t>User is logged in as Staff.
-Currently on Student Management or Internship Management interface.</t>
+Currently on Internship Management interface.</t>
         </is>
       </c>
       <c r="H5" s="9" t="inlineStr">
         <is>
-          <t>Role="Staff"</t>
+          <t>StaffEmail="staff@passerellesnumeriques.org"</t>
         </is>
       </c>
       <c r="I5" s="9" t="inlineStr">
         <is>
-          <t>1. Truy cap interface report cua student bat ky hoac kiem tra cac nut chuc nang tren trang report.</t>
+          <t>1. Access Internship Management interface;
+2. Check for report submission options.</t>
         </is>
       </c>
       <c r="J5" s="9" t="inlineStr">
         <is>
-          <t>Khong xuat hien nut "+ New Report" hoac bat ky tuy select nao allows Staff create internship report.</t>
+          <t>Create Internship Report button is not present for Staff account.</t>
         </is>
       </c>
       <c r="K5" s="9" t="inlineStr"/>
@@ -1654,18 +1655,18 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M5" s="10" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="M5" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="N5" s="9" t="inlineStr">
         <is>
-          <t>Related to User Roles (Section 4), Staff Access (Rule 6.12)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="120" customHeight="1">
+          <t>Related Requirement: M06-F01, Business Rules 6.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="90" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>TC-M06-005</t>
@@ -1673,7 +1674,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Module 06 – Bi-Weekly Internship Reports</t>
+          <t>Module 06 - Bi-Weekly Internship Reports</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -1683,43 +1684,42 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Draft Saving</t>
+          <t>Draft Saving &amp; Editing</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Save temporary report as Draft</t>
+          <t>Save Temporary Report as Draft</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Verify functionality for save as draft report voi thong tin chua day du de edit sau.</t>
+          <t>Verify functionality for saving unfinished report as a draft.</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
           <t>User is logged in as Student.
-Currently on new internship report creation interface.</t>
+Currently on report creation interface.</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>CompanySupervisorName="Nguyen Van B"; StartDate="2026-07-20"; Status="Draft"</t>
+          <t>StartDate="2026-08-03"; Task1="Research documentation"</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>1. Enter Ten supervisor cua company la "Nguyen Van B".
-2. Select Start Date la "2026-07-20" (Monday).
-3. De trong cac truong bat buoc khac.
-4. Nhap nut "Save as Draft" (Save as draft).</t>
+          <t>1. Enter Start Date as "2026-08-03";
+2. Enter task details;
+3. Click Save Draft button.</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>System display notification save as draft successfully.
-Bao cao duoc save vao danh sach voi status "Draft".
-Hoc vien can mo lai de tiep tuc edit.</t>
+          <t>Report is saved with status Draft.
+Success message "Draft saved successfully" appears.
+Data is saved to database without triggering submit validation.</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr"/>
@@ -1735,11 +1735,11 @@
       </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
-          <t>Related to M06-F02, Rule 6.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="165" customHeight="1">
+          <t>Related Requirement: M06-F02, Business Rules 6.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="90" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>TC-M06-006</t>
@@ -1747,7 +1747,7 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Module 06 – Bi-Weekly Internship Reports</t>
+          <t>Module 06 - Bi-Weekly Internship Reports</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
@@ -1757,43 +1757,42 @@
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>Draft Saving</t>
+          <t>Draft Saving &amp; Editing</t>
         </is>
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>Edit draft report unlimited number of times</t>
+          <t>Edit Draft Report Unlimited Number of Times</t>
         </is>
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>Verify whether student can edit va save lai draft report nhieu lan truoc khi submit chinh thuc.</t>
+          <t>Verify student can reopen and edit draft report multiple times before submitting.</t>
         </is>
       </c>
       <c r="G7" s="9" t="inlineStr">
         <is>
           <t>User is logged in as Student.
-Da co san mot report o status "Draft" trong danh sach.</t>
+Existing report with status Draft.</t>
         </is>
       </c>
       <c r="H7" s="9" t="inlineStr">
         <is>
-          <t>ReportId="REP001"; InitialStatus="Draft"; NewSupervisorName="Tran Thi C"; Tasks=[{"TaskName": "Design Database", "Description": "Create ERD", "Result": "Completed"}]</t>
+          <t>UpdatedTask="Updated task documentation"</t>
         </is>
       </c>
       <c r="I7" s="9" t="inlineStr">
         <is>
-          <t>1. Select draft report "REP001" tu danh sach va click "Edit" (Edit).
-2. Thay doi Ten supervisor thanh "Tran Thi C".
-3. Add mot task vao task table.
-4. Nhap nut "Save as Draft".
-5. Mo lai report do lan nua, sua doi thong tin va click "Save as Draft" tiep.</t>
+          <t>1. Open draft report;
+2. Update task details;
+3. Click Save Draft button;
+4. Repeat process multiple times.</t>
         </is>
       </c>
       <c r="J7" s="9" t="inlineStr">
         <is>
-          <t>System allows edit va save successfully tat ca cac thay doi ma without limit times.
-Status report van giu nguyen la "Draft" sau moi lan save as draft.</t>
+          <t>Draft report updates successfully every time without restriction.
+Report status remains Draft.</t>
         </is>
       </c>
       <c r="K7" s="9" t="inlineStr"/>
@@ -1809,11 +1808,11 @@
       </c>
       <c r="N7" s="9" t="inlineStr">
         <is>
-          <t>Related to M06-F02, Rule 6.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="105" customHeight="1">
+          <t>Related Requirement: M06-F02, Business Rules 6.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="90" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>TC-M06-007</t>
@@ -1821,7 +1820,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Module 06 – Bi-Weekly Internship Reports</t>
+          <t>Module 06 - Bi-Weekly Internship Reports</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -1831,39 +1830,41 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Draft Saving</t>
+          <t>Draft Saving &amp; Editing</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Draft report does not send emails and is hidden from Staff</t>
+          <t>Draft Report Does Not Send Emails and Is Hidden from Staff</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Dam bao draft report khong kich hoat tinh nang gui email va cannot nhin thay boi account Staff.</t>
+          <t>Verify saving a draft does not send email notifications and draft is not visible to Staff.</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>Hoc vien vua thuc hien save as draft mot new report.</t>
+          <t>User is logged in as Student.
+Draft report saved.</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>Status="Draft"; StudentEmail="student01@student.passerellesnumeriques.org"; PnvSupervisorEmail="pnv.sup@passerellesnumeriques.org"</t>
+          <t>ReportStatus="Draft"</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>1. Verify hom thu cua PNV Supervisor va Company Supervisor xem co email notification nao duoc gui di khong.
-2. Log in system bang account Staff, access trang chi tiet student (Student Detail) cua student nay va kiem tra danh sach report.</t>
+          <t>1. Save report as Draft;
+2. Log in as Staff and check student report list;
+3. Check email inbox of PNV and Company supervisors.</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>1. Khong co email nao duoc gui tu system.
-2. Tai khoan Staff khong nhin thay draft report nay trong danh sach report cua student.</t>
+          <t>No email notification is sent.
+Draft report is hidden from Staff view.</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr"/>
@@ -1879,11 +1880,11 @@
       </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
-          <t>Related to M06-F02, Rule 6.2, Rule 6.12</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="105" customHeight="1">
+          <t>Related Requirement: M06-F02, Business Rules 6.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
           <t>TC-M06-008</t>
@@ -1891,51 +1892,50 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Module 06 – Bi-Weekly Internship Reports</t>
+          <t>Module 06 - Bi-Weekly Internship Reports</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>M06-F04</t>
+          <t>M06-F03</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>Auto-calculated End Date</t>
+          <t>Automatic Date Calculation</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>Auto-calculate End Date when valid Start Date is entered</t>
+          <t>Auto-calculate End Date When Valid Start Date Is Entered</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>Verify functionality for auto-calculate End Date (End Date) dua tren cong thuc Start Date (Start Date) + 13 ngay.</t>
+          <t>Verify system automatically calculates End Date as Sunday 13 days after Start Date (Monday).</t>
         </is>
       </c>
       <c r="G9" s="9" t="inlineStr">
         <is>
           <t>User is logged in as Student.
-Currently on new report creation interface.</t>
+Currently on report creation interface.</t>
         </is>
       </c>
       <c r="H9" s="9" t="inlineStr">
         <is>
-          <t>StartDate="2026-07-20" (Monday)</t>
+          <t>StartDate="2026-08-03" (Monday)</t>
         </is>
       </c>
       <c r="I9" s="9" t="inlineStr">
         <is>
-          <t>1. Nhap select truong Start Date va enter/select ngay "2026-07-20".
-2. Verify gia tri display o truong End Date.
-3. Thu click dup hoac go vao truong End Date de edit.</t>
+          <t>1. Select Start Date as "2026-08-03";
+2. Observe End Date field.</t>
         </is>
       </c>
       <c r="J9" s="9" t="inlineStr">
         <is>
-          <t>Truong End Date tu dong display ngay "2026-08-02".
-Truong End Date bi vo hieu hoa (disabled/read-only) va user cannot edit thu cong.</t>
+          <t>End Date field automatically fills with "2026-08-16" (Sunday, +13 days).
+End Date field is read-only.</t>
         </is>
       </c>
       <c r="K9" s="9" t="inlineStr"/>
@@ -1951,11 +1951,11 @@
       </c>
       <c r="N9" s="9" t="inlineStr">
         <is>
-          <t>Related to M06-F04, Rule 6.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="120" customHeight="1">
+          <t>Related Requirement: M06-F03, Business Rules 6.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="45" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>TC-M06-009</t>
@@ -1963,52 +1963,50 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Module 06 – Bi-Weekly Internship Reports</t>
+          <t>Module 06 - Bi-Weekly Internship Reports</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>M06-F04</t>
+          <t>M06-F03</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Auto-calculated End Date</t>
+          <t>Automatic Date Calculation</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Prevent submitting report if Start Date is not a Monday</t>
+          <t>Prevent Submitting Report if Start Date Is Not a Monday</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Verify system bao error khi Start Date duoc select khong roi vao thu Hai.</t>
+          <t>Verify system displays error if selected Start Date is not a Monday.</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
           <t>User is logged in as Student.
-Currently on new report creation interface.</t>
+Currently on report creation interface.</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>StartDate="2026-07-21" (Tuesday, not thu Hai); Other required fields valid</t>
+          <t>StartDate="2026-08-04" (Tuesday)</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>1. Enter day du thong tin hop le vao cac truong bat buoc.
-2. Thay doi Start Date thanh "2026-07-21" (Tuesday).
-3. Nhap nut "Submit" (Submit report).
-4. Xac nhan submit trong hop thoai xac nhan.</t>
+          <t>1. Select Start Date as "2026-08-04";
+2. Attempt to save or submit report.</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>System display error cphoto bao Start Date phai la thu Hai (e.g.: "Start Date must be a Monday").
-Bao cao khong duoc submit va status khong doi.</t>
+          <t>System displays error: "Start Date must be a Monday."
+Action is blocked.</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr"/>
@@ -2024,11 +2022,11 @@
       </c>
       <c r="N10" s="4" t="inlineStr">
         <is>
-          <t>Related to Validation Rules (Section 7), Error Handling (Section 8)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="90" customHeight="1">
+          <t>Related Requirement: M06-F03, Business Rules 6.3, Validation Rules (Section 8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="60" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
           <t>TC-M06-010</t>
@@ -2036,52 +2034,50 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Module 06 – Bi-Weekly Internship Reports</t>
+          <t>Module 06 - Bi-Weekly Internship Reports</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>M06-F04</t>
+          <t>M06-F03</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>Auto-calculated End Date</t>
+          <t>Automatic Date Calculation</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>Prevent submitting report if Start Date is outside internship period</t>
+          <t>Prevent Submitting Report if Start Date Is Outside Internship Period</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>Verify system bao error khi student select Start Date outside pham vi period internship da cau hinh.</t>
+          <t>Verify system displays error if Start Date is outside group start/end dates.</t>
         </is>
       </c>
       <c r="G11" s="9" t="inlineStr">
         <is>
           <t>User is logged in as Student.
-Thoi gian internship cua student duoc cau hinh tu "2026-07-01" den "2026-09-30".
-Currently on new report creation interface.</t>
+Group internship period is 2026-06-01 to 2026-08-31.</t>
         </is>
       </c>
       <c r="H11" s="9" t="inlineStr">
         <is>
-          <t>StartDate="2026-06-22" (Monday, truoc period internship); Other required fields valid</t>
+          <t>StartDate="2026-05-25" (Monday before group start)</t>
         </is>
       </c>
       <c r="I11" s="9" t="inlineStr">
         <is>
-          <t>1. Enter day du thong tin hop le vao cac truong bat buoc.
-2. Select Start Date la "2026-06-22".
-3. Nhap nut "Submit" va xac nhan.</t>
+          <t>1. Select Start Date as "2026-05-25";
+2. Attempt to save or submit report.</t>
         </is>
       </c>
       <c r="J11" s="9" t="inlineStr">
         <is>
-          <t>System display notification error requires Start Date phai nam trong period internship (e.g.: "Start Date must be within the internship period").
-Bao cao khong duoc submit.</t>
+          <t>System displays error: "Start Date must fall within the internship group period."
+Action is blocked.</t>
         </is>
       </c>
       <c r="K11" s="9" t="inlineStr"/>
@@ -2097,11 +2093,11 @@
       </c>
       <c r="N11" s="9" t="inlineStr">
         <is>
-          <t>Related to Validation Rules (Section 7), Error Handling (Section 8)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="150" customHeight="1">
+          <t>Related Requirement: M06-F03, Business Rules 6.3, Validation Rules (Section 8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="75" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
           <t>TC-M06-011</t>
@@ -2109,56 +2105,51 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Module 06 – Bi-Weekly Internship Reports</t>
+          <t>Module 06 - Bi-Weekly Internship Reports</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>M06-F05</t>
+          <t>M06-F04</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Dynamic Task Table</t>
+          <t>Dynamic Task Table Management</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Add and remove task rows in dynamic task table</t>
+          <t>Add and Remove Task Rows in Dynamic Task Table</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Verify functionality for add moi task row va delete bot task row hien tai trong task table.</t>
+          <t>Verify functionality for adding new task rows and removing task rows in the report form.</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
           <t>User is logged in as Student.
-Currently on report creation or edit interface.</t>
+Currently on report creation interface.</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>Khong co du lieu dac biet</t>
+          <t>Task1="Frontend UI"; Task2="Backend API"</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>1. Nhap nut "Add Task" (Add task).
-2. Enter thong tin vao task row vua create.
-3. Nhap nut "Add Task" mot lan nua de create dong thu 2.
-4. Enter thong tin cho dong thu 2.
-5. Nhap nut "Remove" (Delete) tai task row thu nhat.</t>
+          <t>1. Click Add Task Row button;
+2. Enter task details in row 2;
+3. Click Remove icon on row 2.</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>1. Mot dong moi xuat hien voi cac o enter: Ten task, Mo ta, Ket qua.
-2. Enter lieu binh thuong.
-3. Dong thu 2 duoc create add.
-4. Enter lieu binh thuong cho dong thu 2.
-5. Dong thu nhat bi delete khoi bang, chi con lai dong thu 2.</t>
+          <t>Clicking Add Task Row appends a new empty task row.
+Clicking Remove deletes row 2 cleanly.</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr"/>
@@ -2174,11 +2165,11 @@
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t>Related to M06-F05, Rule 6.6</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="75" customHeight="1">
+          <t>Related Requirement: M06-F04, UI Standards</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="60" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
           <t>TC-M06-012</t>
@@ -2186,50 +2177,50 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Module 06 – Bi-Weekly Internship Reports</t>
+          <t>Module 06 - Bi-Weekly Internship Reports</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>M06-F05</t>
+          <t>M06-F04</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>Dynamic Task Table</t>
+          <t>Dynamic Task Table Management</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>Prevent submit report khi danh sach task trong</t>
+          <t>Prevent Submitting Report when Task List Is Empty</t>
         </is>
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>Dam bao system bat buoc report phai co it nhat mot task moi allows submit.</t>
+          <t>Verify system blocks submission when report has 0 task rows.</t>
         </is>
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
           <t>User is logged in as Student.
-Dang o interface create new report, cac truong thong tin chung da dien day du.</t>
+Report has all task rows removed.</t>
         </is>
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>TaskList=Empty; Other required fields valid</t>
+          <t>Tasks=[]</t>
         </is>
       </c>
       <c r="I13" s="9" t="inlineStr">
         <is>
-          <t>1. Delete tat ca cac task row trong task table (hoac khong add dong nao).
-2. Nhap nut "Submit" va xac nhan.</t>
+          <t>1. Remove all task rows;
+2. Click Submit Report button.</t>
         </is>
       </c>
       <c r="J13" s="9" t="inlineStr">
         <is>
-          <t>System display notification error requires phai enter it nhat mot task (e.g.: "At least one task is required").
-Bao cao khong duoc submit.</t>
+          <t>System blocks submission.
+Validation error message appears: "At least one task is required."</t>
         </is>
       </c>
       <c r="K13" s="9" t="inlineStr"/>
@@ -2245,11 +2236,11 @@
       </c>
       <c r="N13" s="9" t="inlineStr">
         <is>
-          <t>Related to Validation Rules (Section 7), Error Handling (Section 8)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="90" customHeight="1">
+          <t>Related Requirement: M06-F04, Validation Rules (Section 8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="75" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
           <t>TC-M06-013</t>
@@ -2257,51 +2248,51 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Module 06 – Bi-Weekly Internship Reports</t>
+          <t>Module 06 - Bi-Weekly Internship Reports</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>M06-F05</t>
+          <t>M06-F04</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Dynamic Task Table</t>
+          <t>Dynamic Task Table Management</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>Prevent submit report khi co task row chua hoan thanh thong tin</t>
+          <t>Prevent Submitting Report when Task Row Has Incomplete Details</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Verify system bao error neu ton tai bat ky task row nao bi bo trong Ten, Mo ta hoac Ket qua khi submit.</t>
+          <t>Verify system blocks submission if any task row has empty mandatory fields (Task Description, Hours, etc.).</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
           <t>User is logged in as Student.
-Currently on new report creation interface.</t>
+Task row added with blank Task Description.</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>TaskName="Code FE"; Description=""; Result="Done" (De trong phan Mo ta)</t>
+          <t>TaskDescription=""; Hours=8</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>1. Enter day du thong tin chung hop le.
-2. Add mot task row, enter Ten task la "Code FE", Ket qua la "Done", bo trong Mo ta.
-3. Nhap nut "Submit" va xac nhan.</t>
+          <t>1. Add task row;
+2. Enter hours but leave description empty;
+3. Click Submit Report button.</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>System bao error task row khong hop le (e.g.: "Task fields cannot be left blank").
-Bao cao khong duoc submit.</t>
+          <t>System blocks submission.
+Validation error message appears highlighting required fields in task table.</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr"/>
@@ -2317,11 +2308,11 @@
       </c>
       <c r="N14" s="4" t="inlineStr">
         <is>
-          <t>Related to Rule 6.6, Validation Rules (Section 7), Error Handling (Section 8)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="165" customHeight="1">
+          <t>Related Requirement: M06-F04, Validation Rules (Section 8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="60" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
         <is>
           <t>TC-M06-014</t>
@@ -2329,54 +2320,50 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Module 06 – Bi-Weekly Internship Reports</t>
+          <t>Module 06 - Bi-Weekly Internship Reports</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>M06-F06</t>
+          <t>M06-F05</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>Auto-calculated Total Hours</t>
+          <t>Working Hours Calculation</t>
         </is>
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>Auto-calculate so gio lam viec hang ngay va tong so gio lam viec</t>
+          <t>Auto-calculate Daily Working Hours and Total Working Hours</t>
         </is>
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>Verify functionality for tu dong tinh tong so gio lam viec theo tuan va tong ca ky report khi user enter so gio lam viec hang ngay.</t>
+          <t>Verify system automatically calculates daily working hours and total bi-weekly hours.</t>
         </is>
       </c>
       <c r="G15" s="9" t="inlineStr">
         <is>
           <t>User is logged in as Student.
-Currently on report creation or edit interface.</t>
+Currently on report task table.</t>
         </is>
       </c>
       <c r="H15" s="9" t="inlineStr">
         <is>
-          <t>Week1Hours=[8, 8, 8, 8, 8, 0, 0]; Week2Hours=[8, 8, 8, 8, 8, 4, 0]</t>
+          <t>Week1Hours=[8,8,8,8,8,0,0]; Week2Hours=[8,8,8,8,8,0,0]</t>
         </is>
       </c>
       <c r="I15" s="9" t="inlineStr">
         <is>
-          <t>1. Enter so gio lam viec cho Tuan 1 tu thu Hai den Sunday lan luot la: 8, 8, 8, 8, 8, 0, 0.
-2. Enter so gio lam viec cho Tuan 2 lan luot la: 8, 8, 8, 8, 8, 4, 0.
-3. Observe tong so gio cua Tuan 1, Tuan 2 va Tong so gio lam viec display tren interface.
-4. Thay doi so gio ngay thu Bay Tuan 2 tu 4 thanh 8.</t>
+          <t>1. Enter 8 hours per day for Monday to Friday in both weeks;
+2. Observe Total Hours summary.</t>
         </is>
       </c>
       <c r="J15" s="9" t="inlineStr">
         <is>
-          <t>Tong so gio Tuan 1 tu dong display 40.
-Tong so gio Tuan 2 tu dong display 44.
-Tong so gio lam viec ca ky report tu dong display 84.
-Khi thay doi ngay thu Bay Tuan 2 thanh 8, tong Tuan 2 lap tuc cap nhat thanh 48 va Tong so gio lam viec cap nhat thanh 88.</t>
+          <t>Daily totals sum correctly.
+Total Bi-Weekly Hours automatically calculates to 80 hours.</t>
         </is>
       </c>
       <c r="K15" s="9" t="inlineStr"/>
@@ -2392,11 +2379,11 @@
       </c>
       <c r="N15" s="9" t="inlineStr">
         <is>
-          <t>Related to M06-F06, Rule 6.7</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="75" customHeight="1">
+          <t>Related Requirement: M06-F05, Business Rules 6.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="60" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
           <t>TC-M06-015</t>
@@ -2404,50 +2391,49 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Module 06 – Bi-Weekly Internship Reports</t>
+          <t>Module 06 - Bi-Weekly Internship Reports</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>M06-F06</t>
+          <t>M06-F05</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Auto-calculated Total Hours</t>
+          <t>Working Hours Calculation</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Prevent enter so gio lam viec la so am</t>
+          <t>Prevent Entering Negative Working Hours</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Dam bao system khong chap nhan gia tri so gio lam viec nho hon 0.</t>
+          <t>Verify system blocks negative numbers in working hours inputs.</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>User is logged in as Student.
-Currently on report creation or edit interface.</t>
+          <t>User is logged in as Student.</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>HourInput=-2</t>
+          <t>Hours=-5</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>1. Enter gia tri -2 vao o enter gio lam viec cua ngay bat ky.
-2. Nhan nut "Save as Draft" hoac "Submit".</t>
+          <t>1. Enter -5 into working hours field;
+2. Click Submit or blur field.</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>System bao error so gio khong hop le hoac tu dong khoi phuc ve 0/ngan khong cho enter so am.
-Bao cao khong duoc save/submit voi gia tri am.</t>
+          <t>System blocks negative value.
+Error appears: "Working hours cannot be negative."</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr"/>
@@ -2463,11 +2449,11 @@
       </c>
       <c r="N16" s="4" t="inlineStr">
         <is>
-          <t>Related to Boundary Value Testing (Section 6.7)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="75" customHeight="1">
+          <t>Related Requirement: M06-F05, Validation Rules (Section 8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="60" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
           <t>TC-M06-016</t>
@@ -2475,50 +2461,49 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Module 06 – Bi-Weekly Internship Reports</t>
+          <t>Module 06 - Bi-Weekly Internship Reports</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>M06-F06</t>
+          <t>M06-F05</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>Auto-calculated Total Hours</t>
+          <t>Working Hours Calculation</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
-          <t>Prevent enter so gio lam viec exceeding 24 gio mot ngay</t>
+          <t>Prevent Entering Working Hours Exceeding 24 Hours a Day</t>
         </is>
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>Dam bao system khong chap nhan gia tri so gio lam viec lon hon 24 gio cho mot ngay.</t>
+          <t>Verify system blocks daily working hours greater than 24.</t>
         </is>
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>User is logged in as Student.
-Currently on report creation or edit interface.</t>
+          <t>User is logged in as Student.</t>
         </is>
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>HourInput=25</t>
+          <t>Hours=25</t>
         </is>
       </c>
       <c r="I17" s="9" t="inlineStr">
         <is>
-          <t>1. Enter gia tri 25 vao o enter gio lam viec cua ngay bat ky.
-2. Nhan nut "Save as Draft" hoac "Submit".</t>
+          <t>1. Enter 25 into working hours field for a single day;
+2. Click Submit or blur field.</t>
         </is>
       </c>
       <c r="J17" s="9" t="inlineStr">
         <is>
-          <t>System bao error so gio cannot exceeding 24 gio mot ngay.
-Gia tri khong duoc chap nhan va report khong duoc save/submit.</t>
+          <t>System blocks input.
+Error appears: "Daily working hours cannot exceed 24 hours."</t>
         </is>
       </c>
       <c r="K17" s="9" t="inlineStr"/>
@@ -2534,11 +2519,11 @@
       </c>
       <c r="N17" s="9" t="inlineStr">
         <is>
-          <t>Related to Boundary Value Testing (Section 6.7)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="60" customHeight="1">
+          <t>Related Requirement: M06-F05, Validation Rules (Section 8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="45" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
           <t>TC-M06-017</t>
@@ -2546,49 +2531,47 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Module 06 – Bi-Weekly Internship Reports</t>
+          <t>Module 06 - Bi-Weekly Internship Reports</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>M06-F06</t>
+          <t>M06-F05</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Auto-calculated Total Hours</t>
+          <t>Working Hours Calculation</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>Prevent enter ky tu not so vao o so gio lam viec</t>
+          <t>Prevent Entering Non-numeric Characters into Working Hours Field</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Dam bao system chi chap nhan du lieu so trong o enter so gio lam viec.</t>
+          <t>Verify system restricts working hours inputs to valid numeric values.</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>User is logged in as Student.
-Currently on report creation or edit interface.</t>
+          <t>User is logged in as Student.</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>HourInput="abc"</t>
+          <t>Hours="abc"</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>1. Enter ky tu "abc" vao o enter gio lam viec cua ngay bat ky.
-2. Verify gia tri trong o enter.</t>
+          <t>1. Attempt to type non-numeric text "abc" into working hours field.</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>System tu dong loai bo ky tu chu hoac display error va khong allows enter ky tu phi so.</t>
+          <t>Non-numeric input is prevented or validation error appears: "Please enter a valid number."</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr"/>
@@ -2597,18 +2580,18 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M18" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="M18" s="10" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="N18" s="4" t="inlineStr">
         <is>
-          <t>Related to Boundary Value Testing (Section 6.7)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="165" customHeight="1">
+          <t>Related Requirement: M06-F05, Validation Rules (Section 8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="180" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
         <is>
           <t>TC-M06-018</t>
@@ -2616,12 +2599,12 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Module 06 – Bi-Weekly Internship Reports</t>
+          <t>Module 06 - Bi-Weekly Internship Reports</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>M06-F07</t>
+          <t>M06-F06</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
@@ -2631,37 +2614,41 @@
       </c>
       <c r="E19" s="9" t="inlineStr">
         <is>
-          <t>Submit report successfully voi day du thong tin hop le</t>
+          <t>Submit Report Successfully with Complete Valid Data</t>
         </is>
       </c>
       <c r="F19" s="9" t="inlineStr">
         <is>
-          <t>Verify luong submit report successfully khi dien day du va dung format tat ca cac thong tin bat buoc.</t>
+          <t>Verify functionality for submitting a bi-weekly internship report with complete valid information.</t>
         </is>
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
           <t>User is logged in as Student.
-Dang o interface create internship report.</t>
+Currently on report creation form.</t>
         </is>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>CompanySupervisorName="Nguyen Van B"; StartDate="2026-07-20"; PnvSupervisorEmail="pnv.sup@passerellesnumeriques.org"; CompanySupervisorEmail="company.sup@example.com"; TaskName="Implement Login API"; TaskDesc="Develop authentication feature"; TaskResult="Completed successfully"; Week1Hours=[8,8,8,8,8,0,0]; Week2Hours=[8,8,8,8,8,0,0]; Challenges="Gap kho khan khi tich hop OAuth"; SupportNeeded="Can mentor ho tro review code"</t>
+          <t>StartDate="2026-08-03"; CompanySupervisorName="John Doe"; CompanySupervisorEmail="john@company.com"; PnvSupervisorEmail="mentor@passerellesnumeriques.org"; Challenges="None"; SupportNeeded="None"</t>
         </is>
       </c>
       <c r="I19" s="9" t="inlineStr">
         <is>
-          <t>1. Dien day du thong tin nhu trong Test Data.
-2. Nhan nut "Submit" (Submit report).
-3. Tai hop thoai xac nhan "Submit Report", click button "Confirm" (Xac nhan).</t>
+          <t>1. Enter valid Start Date "2026-08-03";
+2. Complete task table details;
+3. Enter valid Company Supervisor Name and Email;
+4. Enter valid PNV Supervisor Email;
+5. Enter Challenges and Support Needed;
+6. Click Submit Report button;
+7. Confirm submission in popup dialog.</t>
         </is>
       </c>
       <c r="J19" s="9" t="inlineStr">
         <is>
-          <t>System display notification submit report successfully.
-Status cua report chuyen sang "Submitted".
-Bao cao chuyen sang che do chi doc.</t>
+          <t>Report is submitted successfully.
+Report status changes to Submitted.
+Success notification appears and page transitions to View mode.</t>
         </is>
       </c>
       <c r="K19" s="9" t="inlineStr"/>
@@ -2677,11 +2664,11 @@
       </c>
       <c r="N19" s="9" t="inlineStr">
         <is>
-          <t>Related to M06-F07, Rule 6.3</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="75" customHeight="1">
+          <t>Related Requirement: M06-F06, Business Rules 6.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="60" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
           <t>TC-M06-019</t>
@@ -2689,50 +2676,49 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Module 06 – Bi-Weekly Internship Reports</t>
+          <t>Module 06 - Bi-Weekly Internship Reports</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>M06-F03</t>
+          <t>M06-F06</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Submission Validation</t>
+          <t>Report Submission</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>Submit report failed due to empty name nguoi supervisor company</t>
+          <t>Submit Report Fails Due to Empty Company Supervisor Name</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Verify system bao error khi blank truong Ten supervisor cua company.</t>
+          <t>Verify system blocks report submission when Company Supervisor Name is empty.</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>User is logged in as Student.
-Currently on new report creation interface.</t>
+          <t>User is logged in as Student.</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>CompanySupervisorName=""; Cac truong khac deu hop le</t>
+          <t>CompanySupervisorName=""</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>1. Dien day du thong tin hop le tru truong Ten supervisor company blank.
-2. Nhap nut "Submit" va xac nhan.</t>
+          <t>1. Fill report details but leave Company Supervisor Name blank;
+2. Click Submit Report button.</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>System bao error requires enter Ten supervisor company (e.g.: "Company Supervisor Name is required").
-Bao cao khong duoc submit.</t>
+          <t>System blocks submission.
+Validation error message appears: "Company Supervisor Name is required."</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr"/>
@@ -2748,11 +2734,11 @@
       </c>
       <c r="N20" s="4" t="inlineStr">
         <is>
-          <t>Related to Validation Rules (Section 7), Error Handling (Section 8)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="75" customHeight="1">
+          <t>Related Requirement: M06-F06, Validation Rules (Section 8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="60" customHeight="1">
       <c r="A21" s="7" t="inlineStr">
         <is>
           <t>TC-M06-020</t>
@@ -2760,50 +2746,49 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Module 06 – Bi-Weekly Internship Reports</t>
+          <t>Module 06 - Bi-Weekly Internship Reports</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>M06-F03</t>
+          <t>M06-F06</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>Submission Validation</t>
+          <t>Report Submission</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>Submit report failed do blank email nguoi supervisor PNV</t>
+          <t>Submit Report Fails Due to Blank PNV Supervisor Email</t>
         </is>
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>Verify system bao error khi blank truong Email supervisor PNV.</t>
+          <t>Verify system blocks report submission when PNV Supervisor Email is empty.</t>
         </is>
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
-          <t>User is logged in as Student.
-Currently on new report creation interface.</t>
+          <t>User is logged in as Student.</t>
         </is>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
-          <t>PnvSupervisorEmail=""; Cac truong khac deu hop le</t>
+          <t>PnvSupervisorEmail=""</t>
         </is>
       </c>
       <c r="I21" s="9" t="inlineStr">
         <is>
-          <t>1. Dien day du thong tin hop le tru truong Email supervisor PNV blank.
-2. Nhap nut "Submit" va xac nhan.</t>
+          <t>1. Fill report details but leave PNV Supervisor Email blank;
+2. Click Submit Report button.</t>
         </is>
       </c>
       <c r="J21" s="9" t="inlineStr">
         <is>
-          <t>System bao error requires enter Email supervisor PNV (e.g.: "PNV Supervisor Email is required").
-Bao cao khong duoc submit.</t>
+          <t>System blocks submission.
+Validation error message appears: "PNV Supervisor Email is required."</t>
         </is>
       </c>
       <c r="K21" s="9" t="inlineStr"/>
@@ -2819,11 +2804,11 @@
       </c>
       <c r="N21" s="9" t="inlineStr">
         <is>
-          <t>Related to Validation Rules (Section 7), Error Handling (Section 8)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="75" customHeight="1">
+          <t>Related Requirement: M06-F06, Validation Rules (Section 8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="60" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
           <t>TC-M06-021</t>
@@ -2831,50 +2816,49 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Module 06 – Bi-Weekly Internship Reports</t>
+          <t>Module 06 - Bi-Weekly Internship Reports</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>M06-F03</t>
+          <t>M06-F06</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>Submission Validation</t>
+          <t>Report Submission</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>Submit report failed do email nguoi supervisor PNV sai format</t>
+          <t>Submit Report Fails Due to Invalid PNV Supervisor Email Format</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Verify system bao error khi enter email supervisor PNV khong dung format.</t>
+          <t>Verify system blocks submission when PNV Supervisor Email has invalid format.</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>User is logged in as Student.
-Currently on new report creation interface.</t>
+          <t>User is logged in as Student.</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>PnvSupervisorEmail="pnv.sup"; Cac truong khac deu hop le</t>
+          <t>PnvSupervisorEmail="invalid-email"</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>1. Dien day du thong tin hop le tru truong Email supervisor PNV enter la "pnv.sup".
-2. Nhap nut "Submit" va xac nhan.</t>
+          <t>1. Enter invalid email format "invalid-email" for PNV Supervisor Email;
+2. Click Submit Report button.</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>System bao error format Email supervisor PNV khong hop le (e.g.: "Invalid PNV Supervisor Email format").
-Bao cao khong duoc submit.</t>
+          <t>System blocks submission.
+Validation error message appears: "Invalid email address format."</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr"/>
@@ -2890,11 +2874,11 @@
       </c>
       <c r="N22" s="4" t="inlineStr">
         <is>
-          <t>Related to Validation Rules (Section 7), Error Handling (Section 8)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="75" customHeight="1">
+          <t>Related Requirement: M06-F06, Validation Rules (Section 8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="60" customHeight="1">
       <c r="A23" s="7" t="inlineStr">
         <is>
           <t>TC-M06-022</t>
@@ -2902,50 +2886,49 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Module 06 – Bi-Weekly Internship Reports</t>
+          <t>Module 06 - Bi-Weekly Internship Reports</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>M06-F03</t>
+          <t>M06-F06</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>Submission Validation</t>
+          <t>Report Submission</t>
         </is>
       </c>
       <c r="E23" s="9" t="inlineStr">
         <is>
-          <t>Submit report failed do blank email nguoi supervisor company</t>
+          <t>Submit Report Fails Due to Blank Company Supervisor Email</t>
         </is>
       </c>
       <c r="F23" s="9" t="inlineStr">
         <is>
-          <t>Verify system bao error khi blank truong Email supervisor company.</t>
+          <t>Verify system blocks report submission when Company Supervisor Email is empty.</t>
         </is>
       </c>
       <c r="G23" s="9" t="inlineStr">
         <is>
-          <t>User is logged in as Student.
-Currently on new report creation interface.</t>
+          <t>User is logged in as Student.</t>
         </is>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
-          <t>CompanySupervisorEmail=""; Cac truong khac deu hop le</t>
+          <t>CompanySupervisorEmail=""</t>
         </is>
       </c>
       <c r="I23" s="9" t="inlineStr">
         <is>
-          <t>1. Dien day du thong tin hop le tru truong Email supervisor company blank.
-2. Nhap nut "Submit" va xac nhan.</t>
+          <t>1. Fill report details but leave Company Supervisor Email blank;
+2. Click Submit Report button.</t>
         </is>
       </c>
       <c r="J23" s="9" t="inlineStr">
         <is>
-          <t>System bao error requires co it nhat mot email supervisor company (e.g.: "Company Supervisor Email is required").
-Bao cao khong duoc submit.</t>
+          <t>System blocks submission.
+Validation error message appears: "Company Supervisor Email is required."</t>
         </is>
       </c>
       <c r="K23" s="9" t="inlineStr"/>
@@ -2961,11 +2944,11 @@
       </c>
       <c r="N23" s="9" t="inlineStr">
         <is>
-          <t>TRUNG LAP. Test case nay trung lap voi requires "At least one valid email address" da duoc kiem tra. Nen duoc loai bo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="75" customHeight="1">
+          <t>Related Requirement: M06-F06, Validation Rules (Section 8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="60" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
           <t>TC-M06-023</t>
@@ -2973,50 +2956,49 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Module 06 – Bi-Weekly Internship Reports</t>
+          <t>Module 06 - Bi-Weekly Internship Reports</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>M06-F03</t>
+          <t>M06-F06</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>Submission Validation</t>
+          <t>Report Submission</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>Submit report failed do email nguoi supervisor company sai format</t>
+          <t>Submit Report Fails Due to Invalid Company Supervisor Email Format</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Verify system bao error khi enter email supervisor company khong dung format email.</t>
+          <t>Verify system blocks submission when Company Supervisor Email has invalid format.</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>User is logged in as Student.
-Currently on new report creation interface.</t>
+          <t>User is logged in as Student.</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>CompanySupervisorEmail="company.sup@"; Cac truong khac deu hop le</t>
+          <t>CompanySupervisorEmail="invalid-email"</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>1. Dien day du thong tin hop le tru truong Email supervisor company enter la "company.sup@".
-2. Nhap nut "Submit" va xac nhan.</t>
+          <t>1. Enter invalid email format "invalid-email" for Company Supervisor Email;
+2. Click Submit Report button.</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>System bao error format Email supervisor company khong hop le (e.g.: "Invalid Company Supervisor Email format").
-Bao cao khong duoc submit.</t>
+          <t>System blocks submission.
+Validation error message appears: "Invalid email address format."</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr"/>
@@ -3032,7 +3014,7 @@
       </c>
       <c r="N24" s="4" t="inlineStr">
         <is>
-          <t>Related to Validation Rules (Section 7), Error Handling (Section 8)</t>
+          <t>Related Requirement: M06-F06, Validation Rules (Section 8)</t>
         </is>
       </c>
     </row>
@@ -3044,50 +3026,49 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Module 06 – Bi-Weekly Internship Reports</t>
+          <t>Module 06 - Bi-Weekly Internship Reports</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>M06-F03</t>
+          <t>M06-F06</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>Submission Validation</t>
+          <t>Report Submission</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
-          <t>Submit report failed do blank phan mo ta kho khan (Challenges)</t>
+          <t>Submit Report Fails Due to Blank Challenges Section</t>
         </is>
       </c>
       <c r="F25" s="9" t="inlineStr">
         <is>
-          <t>Verify system bao error khi truong Kho khan gap phai (Challenges) bi bo trong khi submit.</t>
+          <t>Verify system blocks report submission when Challenges field is empty.</t>
         </is>
       </c>
       <c r="G25" s="9" t="inlineStr">
         <is>
-          <t>User is logged in as Student.
-Currently on new report creation interface.</t>
+          <t>User is logged in as Student.</t>
         </is>
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
-          <t>Challenges=""; Cac truong khac deu hop le</t>
+          <t>Challenges=""</t>
         </is>
       </c>
       <c r="I25" s="9" t="inlineStr">
         <is>
-          <t>1. Dien day du thong tin hop le tru truong Kho khan blank.
-2. Nhap nut "Submit" va xac nhan.</t>
+          <t>1. Leave Challenges field blank;
+2. Click Submit Report button.</t>
         </is>
       </c>
       <c r="J25" s="9" t="inlineStr">
         <is>
-          <t>System bao error requires enter Kho khan gap phai (e.g.: "Challenges field is required").
-Bao cao khong duoc submit.</t>
+          <t>System blocks submission.
+Validation error message appears: "Challenges field is required."</t>
         </is>
       </c>
       <c r="K25" s="9" t="inlineStr"/>
@@ -3103,7 +3084,7 @@
       </c>
       <c r="N25" s="9" t="inlineStr">
         <is>
-          <t>Related to Validation Rules (Section 7), Error Handling (Section 8)</t>
+          <t>Related Requirement: M06-F06, Validation Rules (Section 8)</t>
         </is>
       </c>
     </row>
@@ -3115,50 +3096,49 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Module 06 – Bi-Weekly Internship Reports</t>
+          <t>Module 06 - Bi-Weekly Internship Reports</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>M06-F03</t>
+          <t>M06-F06</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>Submission Validation</t>
+          <t>Report Submission</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>Submit report failed do blank phan ho tro can thiet (Support Needed)</t>
+          <t>Submit Report Fails Due to Blank Support Needed Section</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Verify system bao error khi truong Ho tro can thiet (Support Needed) bi bo trong khi submit.</t>
+          <t>Verify system blocks report submission when Support Needed field is empty.</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>User is logged in as Student.
-Currently on new report creation interface.</t>
+          <t>User is logged in as Student.</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>SupportNeeded=""; Cac truong khac deu hop le</t>
+          <t>SupportNeeded=""</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>1. Dien day du thong tin hop le tru truong Ho tro can thiet blank.
-2. Nhap nut "Submit" va xac nhan.</t>
+          <t>1. Leave Support Needed field blank;
+2. Click Submit Report button.</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>System bao error requires enter Ho tro can thiet (e.g.: "Support Needed field is required").
-Bao cao khong duoc submit.</t>
+          <t>System blocks submission.
+Validation error message appears: "Support Needed field is required."</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr"/>
@@ -3174,11 +3154,11 @@
       </c>
       <c r="N26" s="4" t="inlineStr">
         <is>
-          <t>Related to Validation Rules (Section 7), Error Handling (Section 8)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="90" customHeight="1">
+          <t>Related Requirement: M06-F06, Validation Rules (Section 8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="60" customHeight="1">
       <c r="A27" s="7" t="inlineStr">
         <is>
           <t>TC-M06-026</t>
@@ -3186,51 +3166,50 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Module 06 – Bi-Weekly Internship Reports</t>
+          <t>Module 06 - Bi-Weekly Internship Reports</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>M06-F03</t>
+          <t>M06-F06</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>Submission Validation</t>
+          <t>Report Submission</t>
         </is>
       </c>
       <c r="E27" s="9" t="inlineStr">
         <is>
-          <t>Huy xac nhan submit report</t>
+          <t>Cancel Report Submission Confirmation</t>
         </is>
       </c>
       <c r="F27" s="9" t="inlineStr">
         <is>
-          <t>Dam bao system khong submit report neu user click button Huy (Cancel) tren hop thoai xac nhan submit.</t>
+          <t>Verify clicking Cancel in submission confirmation popup returns to edit form without submitting.</t>
         </is>
       </c>
       <c r="G27" s="9" t="inlineStr">
         <is>
           <t>User is logged in as Student.
-Dang o interface create report va da enter day du thong tin hop le.</t>
+Form filled with complete valid data.</t>
         </is>
       </c>
       <c r="H27" s="9" t="inlineStr">
         <is>
-          <t>Cac thong tin hop le</t>
+          <t>Action="Cancel Confirmation"</t>
         </is>
       </c>
       <c r="I27" s="9" t="inlineStr">
         <is>
-          <t>1. Nhap nut "Submit".
-2. Khi hop thoai xac nhan "Submit Report" hien len, click button "Cancel" (Huy) hoac nut dong hop thoai.</t>
+          <t>1. Click Submit Report button;
+2. When confirmation popup appears, click Cancel button.</t>
         </is>
       </c>
       <c r="J27" s="9" t="inlineStr">
         <is>
-          <t>Hop thoai dong lai.
-Bao cao khong duoc submit va status van la draft hoac chua save.
-Nguoi dung van can tiep tuc edit report.</t>
+          <t>Confirmation popup closes.
+Report is not submitted and remains in edit form.</t>
         </is>
       </c>
       <c r="K27" s="9" t="inlineStr"/>
@@ -3246,11 +3225,11 @@
       </c>
       <c r="N27" s="9" t="inlineStr">
         <is>
-          <t>Related to Rule 6.3, Workflow</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="105" customHeight="1">
+          <t>Related Requirement: M06-F06, UI Standards</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="75" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
           <t>TC-M06-027</t>
@@ -3258,7 +3237,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Module 06 – Bi-Weekly Internship Reports</t>
+          <t>Module 06 - Bi-Weekly Internship Reports</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -3268,23 +3247,23 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Report Submission</t>
+          <t>Read-only Submitted Reports</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>Bao cao da submit chuyen sang status chi doc mai mai</t>
+          <t>Submitted Report Permanently Switches to Read-Only Status</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Dam bao report sau khi submit (Submitted) se bi khoa, cannot edit hay delete boi student.</t>
+          <t>Verify student cannot edit or resubmit a report once it has been submitted.</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
           <t>User is logged in as Student.
-Co mot report trong danh sach da o status "Submitted".</t>
+Report status is Submitted.</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
@@ -3294,16 +3273,15 @@
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>1. Mo xem chi tiet report da submit.
-2. Verify su xuat hien cua nut "Edit" (Edit), "Save" (Save), hoac "Delete" (Delete).
-3. Thu click dup hoac thay doi noi dung cac truong thong tin.</t>
+          <t>1. Open submitted report;
+2. Observe UI for edit/save buttons.</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>Nut "Edit" va "Save as Draft" not displayed.
-Tat ca cac truong thong tin deu o status chi doc (disabled/read-only).
-Hoc vien cannot sua doi bat ky du lieu nao.</t>
+          <t>Report displays in Read-Only mode.
+Edit and Save buttons are hidden or disabled.
+Student cannot modify content.</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr"/>
@@ -3319,11 +3297,11 @@
       </c>
       <c r="N28" s="4" t="inlineStr">
         <is>
-          <t>Related to M06-F07, Rule 6.3, Rule 6.11</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="180" customHeight="1">
+          <t>Related Requirement: M06-F07, Business Rules 6.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="60" customHeight="1">
       <c r="A29" s="7" t="inlineStr">
         <is>
           <t>TC-M06-028</t>
@@ -3331,7 +3309,7 @@
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>Module 06 – Bi-Weekly Internship Reports</t>
+          <t>Module 06 - Bi-Weekly Internship Reports</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
@@ -3341,43 +3319,39 @@
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>Automatic Email Notification</t>
+          <t>Automated Email Notifications</t>
         </is>
       </c>
       <c r="E29" s="9" t="inlineStr">
         <is>
-          <t>Gui email notification tu dong khi submit report successfully</t>
+          <t>Send Automatic Email Notification Upon Successful Report Submission</t>
         </is>
       </c>
       <c r="F29" s="9" t="inlineStr">
         <is>
-          <t>Verify whether system co tu dong gui email voi dung format va dung doi tuong sau khi submit report hay khong.</t>
+          <t>Verify system triggers email notifications to PNV supervisor and Company supervisor after successful submission.</t>
         </is>
       </c>
       <c r="G29" s="9" t="inlineStr">
         <is>
-          <t>Nguoi dung da log in voi quyen Student ten "Nguyen Van A", lop "PNV26A", lam viec tai company "TechCorp".
-System ket noi email hoat dong binh thuong.</t>
+          <t>User is logged in as Student.
+Email notification service enabled.</t>
         </is>
       </c>
       <c r="H29" s="9" t="inlineStr">
         <is>
-          <t>StudentName="Nguyen Van A"; BatchName="PNV26A"; Company="TechCorp"; PnvSupervisorEmail="pnv.sup@passerellesnumeriques.org"; CompanySupervisorEmail="company.sup@example.com"; StudentEmail="student01@student.passerellesnumeriques.org"; StartDate="2026-07-20"; EndDate="2026-08-02"</t>
+          <t>PnvSupervisorEmail="mentor@passerellesnumeriques.org"; CompanySupervisorEmail="john@company.com"</t>
         </is>
       </c>
       <c r="I29" s="9" t="inlineStr">
         <is>
-          <t>1. Dien day du thong tin report cua student "Nguyen Van A" lam viec tai "TechCorp" tu ngay "2026-07-20" den "2026-08-02".
-2. Nhap nut "Submit" va xac nhan submit report.
-3. Verify email nhan duoc tu account PNV Supervisor, Company Supervisor va student.</t>
+          <t>1. Submit bi-weekly internship report successfully;
+2. Check email inbox of PNV supervisor and Company supervisor.</t>
         </is>
       </c>
       <c r="J29" s="9" t="inlineStr">
         <is>
-          <t>1. Bao cao submit successfully.
-2. Email duoc tu dong gui den dia chi "pnv.sup@passerellesnumeriques.org" va "company.sup@example.com".
-3. Email duoc gui CC cho "student01@student.passerellesnumeriques.org" va "ero.vietnam@passerellesnumeriques.org".
-4. Tieu de email co format chinh xac: "[PNV26A] [Bi-Weekly Internship Report] Nguyen Van A - TechCorp (Period: 20/07 – 02/08)"</t>
+          <t>Automated email notification is delivered to both supervisor email addresses containing report summary.</t>
         </is>
       </c>
       <c r="K29" s="9" t="inlineStr"/>
@@ -3393,11 +3367,11 @@
       </c>
       <c r="N29" s="9" t="inlineStr">
         <is>
-          <t>Related to M06-F08, Rule 6.10</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="120" customHeight="1">
+          <t>Related Requirement: M06-F08, Business Rules 6.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="75" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
           <t>TC-M06-029</t>
@@ -3405,7 +3379,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Module 06 – Bi-Weekly Internship Reports</t>
+          <t>Module 06 - Bi-Weekly Internship Reports</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -3415,41 +3389,40 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>Automatic Email Notification</t>
+          <t>Automated Email Notifications</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>Xu ly error khi gui email notification failed</t>
+          <t>Handle Error When Email Notification Sending Fails</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>Dam bao system van ghi nhan submit report successfully va display cphoto bao neu qua trinh gui email tu dong bi error.</t>
+          <t>Verify report submission still succeeds and logs error gracefully if email service fails.</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
           <t>User is logged in as Student.
-System email bi error ket noi hoac account gui bi chan.</t>
+Email notification service is temporarily unavailable.</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>Cac thong tin hop le</t>
+          <t>EmailServiceStatus="Offline"</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>1. Dien day du thong tin report hop le.
-2. Nhap nut "Submit" va xac nhan submit report.</t>
+          <t>1. Submit report when email service is offline;
+2. Observe system response.</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>System display cphoto bao error gui email (e.g.: "Email notification failed: [Reason]").
-Bao cao van duoc submit successfully va status chuyen sang "Submitted" binh thuong.
-Du lieu report bi khoa thanh chi doc.</t>
+          <t>Report submission succeeds and saves to database.
+Warning message appears notifying student that email delivery failed, and error is logged.</t>
         </is>
       </c>
       <c r="K30" s="4" t="inlineStr"/>
@@ -3458,18 +3431,18 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="M30" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="M30" s="10" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="N30" s="4" t="inlineStr">
         <is>
-          <t>Related to Rule 6.11, Error Handling (Section 8)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="120" customHeight="1">
+          <t>Related Requirement: M06-F08, Error Handling (Section 8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="75" customHeight="1">
       <c r="A31" s="7" t="inlineStr">
         <is>
           <t>TC-M06-030</t>
@@ -3477,7 +3450,7 @@
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>Module 06 – Bi-Weekly Internship Reports</t>
+          <t>Module 06 - Bi-Weekly Internship Reports</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
@@ -3487,42 +3460,40 @@
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>Staff View of Student Reports</t>
+          <t>Staff Report Viewing</t>
         </is>
       </c>
       <c r="E31" s="9" t="inlineStr">
         <is>
-          <t>Staff xem internship report cua student</t>
+          <t>Staff View Student Internship Report</t>
         </is>
       </c>
       <c r="F31" s="9" t="inlineStr">
         <is>
-          <t>Verify whether account Staff can xem duoc noi dung chi tiet report da submit cua student hay khong.</t>
+          <t>Verify Staff can view submitted bi-weekly internship reports of students.</t>
         </is>
       </c>
       <c r="G31" s="9" t="inlineStr">
         <is>
           <t>User is logged in as Staff.
-Hoc vien "Nguyen Van A" da submit internship report.</t>
+Student has submitted a bi-weekly report.</t>
         </is>
       </c>
       <c r="H31" s="9" t="inlineStr">
         <is>
-          <t>StudentName="Nguyen Van A"; ReportStatus="Submitted"</t>
+          <t>StaffEmail="staff@passerellesnumeriques.org"</t>
         </is>
       </c>
       <c r="I31" s="9" t="inlineStr">
         <is>
-          <t>1. Log in voi quyen Staff.
-2. Truy cap vao trang chi tiet student "Nguyen Van A".
-3. Tim phan Bao cao internship cua student.
-4. Nhap vao xem chi tiet report da submit.</t>
+          <t>1. Access Internship Management interface;
+2. Select student report list;
+3. Click View on student's submitted report.</t>
         </is>
       </c>
       <c r="J31" s="9" t="inlineStr">
         <is>
-          <t>Staff can xem day du noi dung chi tiet cua report student da submit.
-Bao cao display chinh xac cac thong tin student da dien.</t>
+          <t>Staff can view complete report content (tasks, hours, challenges, supervisor info) in Read-Only mode.</t>
         </is>
       </c>
       <c r="K31" s="9" t="inlineStr"/>
@@ -3538,11 +3509,11 @@
       </c>
       <c r="N31" s="9" t="inlineStr">
         <is>
-          <t>Related to M06-F09, Rule 6.12</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="90" customHeight="1">
+          <t>Related Requirement: M06-F09, Business Rules 6.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="60" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
           <t>TC-M06-031</t>
@@ -3550,7 +3521,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Module 06 – Bi-Weekly Internship Reports</t>
+          <t>Module 06 - Bi-Weekly Internship Reports</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -3560,40 +3531,40 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>Staff View of Student Reports</t>
+          <t>Staff Report Viewing</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>Staff cannot sua hoac delete report cua student</t>
+          <t>Staff Cannot Edit or Delete Student Report</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>Dam bao Staff chi co quyen xem (Read-only) va cannot thay doi thong tin hoac delete report cua student.</t>
+          <t>Verify Staff users cannot modify or delete submitted student reports.</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
           <t>User is logged in as Staff.
-Dang o man hinh xem chi tiet report cua student "Nguyen Van A".</t>
+Viewing submitted student report.</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>StudentName="Nguyen Van A"</t>
+          <t>StaffEmail="staff@passerellesnumeriques.org"</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>1. Verify su xuat hien cua cac nut edit (Edit), save (Save), hoac delete (Delete) report.
-2. Thu thay doi gia tri trong cac truong thong tin cua report student.</t>
+          <t>1. Open student submitted report;
+2. Check for edit/delete controls.</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>Khong co bat ky nut hoac tuy select edit/delete nao display voi account Staff.
-Tat ca cac truong thong tin deu bi khoa, cannot tuong tac thay doi gia tri.</t>
+          <t>No edit or delete buttons are available for Staff.
+Report content is strictly Read-Only.</t>
         </is>
       </c>
       <c r="K32" s="4" t="inlineStr"/>
@@ -3609,7 +3580,7 @@
       </c>
       <c r="N32" s="4" t="inlineStr">
         <is>
-          <t>Related to Staff Access (Rule 6.12)</t>
+          <t>Related Requirement: M06-F09, Business Rules 6.8</t>
         </is>
       </c>
     </row>

--- a/Tests/excel/module06_test_cases.xlsx
+++ b/Tests/excel/module06_test_cases.xlsx
@@ -2,31 +2,137 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Report" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Module06" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Module06'!$A$1:$N$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Module06'!$A$1:$N$30</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="18">
+  <fonts count="33">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="FF1F4E78"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="FF137333"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="FFA50E0E"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="FFB06000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="FF1F4E78"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <i val="1"/>
+      <color rgb="FF555555"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="FF64748B"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="FF1E293B"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="FF1F4E78"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="FFA50E0E"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="FFB06000"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="FF137333"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="FF1F4E78"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001F4E78"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <i val="1"/>
+      <color rgb="00555555"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Segoe UI"/>
@@ -48,12 +154,6 @@
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
-      <color rgb="0064748B"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <b val="1"/>
       <color rgb="00A50E0E"/>
       <sz val="10"/>
     </font>
@@ -61,18 +161,6 @@
       <name val="Segoe UI"/>
       <b val="1"/>
       <color rgb="00B06000"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <b val="1"/>
-      <color rgb="001F4E78"/>
-      <sz val="16"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <i val="1"/>
-      <color rgb="00555555"/>
       <sz val="10"/>
     </font>
     <font>
@@ -130,7 +218,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="16">
     <fill>
       <patternFill/>
     </fill>
@@ -139,8 +227,62 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
+        <bgColor rgb="FF1F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6F4EA"/>
+        <bgColor rgb="FFE6F4EA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE8E6"/>
+        <bgColor rgb="FFFCE8E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8FAFC"/>
+        <bgColor rgb="FFF8FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEF7E0"/>
+        <bgColor rgb="FFFEF7E0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2E8F0"/>
+        <bgColor rgb="FFE2E8F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F5F9"/>
+        <bgColor rgb="FFF1F5F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
         <bgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8FAFC"/>
+        <bgColor rgb="00F8FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2E8F0"/>
+        <bgColor rgb="00E2E8F0"/>
       </patternFill>
     </fill>
     <fill>
@@ -157,20 +299,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8FAFC"/>
-        <bgColor rgb="00F8FAFC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FEF7E0"/>
         <bgColor rgb="00FEF7E0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E2E8F0"/>
-        <bgColor rgb="00E2E8F0"/>
       </patternFill>
     </fill>
     <fill>
@@ -180,12 +310,42 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCBD5E1"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFCBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCBD5E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCBD5E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCBD5E1"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFCBD5E1"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF1E293B"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF1E293B"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -220,7 +380,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -254,25 +414,25 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -291,7 +451,7 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -309,21 +469,90 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="11" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="13" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="14" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="15" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -438,12 +667,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Report'!$A$9:$A$17</f>
+              <f>'Report'!$A$9:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Report'!$C$9:$C$17</f>
+              <f>'Report'!$C$9:$C$16</f>
             </numRef>
           </val>
         </ser>
@@ -465,12 +694,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Report'!$A$9:$A$17</f>
+              <f>'Report'!$A$9:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Report'!$D$9:$D$17</f>
+              <f>'Report'!$D$9:$D$16</f>
             </numRef>
           </val>
         </ser>
@@ -492,12 +721,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Report'!$A$9:$A$17</f>
+              <f>'Report'!$A$9:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Report'!$E$9:$E$17</f>
+              <f>'Report'!$E$9:$E$16</f>
             </numRef>
           </val>
         </ser>
@@ -884,7 +1113,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -896,383 +1125,355 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="36" t="inlineStr">
         <is>
           <t>Module 06 - Feature &amp; Priority Summary Report</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="37" t="inlineStr">
         <is>
           <t>Summary of test cases per feature, calculated via Excel formulas</t>
         </is>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="38" t="inlineStr">
         <is>
           <t>Total Features</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="38" t="inlineStr">
         <is>
           <t>Total Test Cases</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="38" t="inlineStr">
         <is>
           <t>High Priority Features</t>
         </is>
       </c>
-      <c r="D4" s="13" t="inlineStr">
+      <c r="D4" s="38" t="inlineStr">
         <is>
           <t>Medium Priority Features</t>
         </is>
       </c>
-      <c r="E4" s="13" t="inlineStr">
+      <c r="E4" s="38" t="inlineStr">
         <is>
           <t>Low Priority Features</t>
         </is>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="14">
-        <f>COUNTA(A9:A17)</f>
-        <v/>
-      </c>
-      <c r="B5" s="15">
-        <f>F18</f>
-        <v/>
-      </c>
-      <c r="C5" s="16">
-        <f>COUNTIF(C9:C17, "&gt;0")</f>
-        <v/>
-      </c>
-      <c r="D5" s="17">
-        <f>COUNTIFS(C9:C17, 0, D9:D17, "&gt;0")</f>
-        <v/>
-      </c>
-      <c r="E5" s="18">
-        <f>COUNTIFS(C9:C17, 0, D9:D17, 0, E9:E17, "&gt;0")</f>
+      <c r="A5" s="39">
+        <f>COUNTA(A9:A16)</f>
+        <v/>
+      </c>
+      <c r="B5" s="40">
+        <f>F17</f>
+        <v/>
+      </c>
+      <c r="C5" s="41">
+        <f>COUNTIF(C9:C16, "&gt;0")</f>
+        <v/>
+      </c>
+      <c r="D5" s="42">
+        <f>COUNTIFS(C9:C16, 0, D9:D16, "&gt;0")</f>
+        <v/>
+      </c>
+      <c r="E5" s="43">
+        <f>COUNTIFS(C9:C16, 0, D9:D16, 0, E9:E16, "&gt;0")</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="19" t="inlineStr">
+      <c r="A7" s="44" t="inlineStr">
         <is>
           <t>Feature Categorization &amp; Priority Breakdown</t>
         </is>
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="20" t="inlineStr">
+      <c r="A8" s="45" t="inlineStr">
         <is>
           <t>Feature ID</t>
         </is>
       </c>
-      <c r="B8" s="21" t="inlineStr">
+      <c r="B8" s="46" t="inlineStr">
         <is>
           <t>Feature Name</t>
         </is>
       </c>
-      <c r="C8" s="20" t="inlineStr">
+      <c r="C8" s="45" t="inlineStr">
         <is>
           <t>High Priority</t>
         </is>
       </c>
-      <c r="D8" s="20" t="inlineStr">
+      <c r="D8" s="45" t="inlineStr">
         <is>
           <t>Medium Priority</t>
         </is>
       </c>
-      <c r="E8" s="20" t="inlineStr">
+      <c r="E8" s="45" t="inlineStr">
         <is>
           <t>Low Priority</t>
         </is>
       </c>
-      <c r="F8" s="20" t="inlineStr">
+      <c r="F8" s="45" t="inlineStr">
         <is>
           <t>Total TCs</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="22" t="inlineStr">
+      <c r="A9" s="47" t="inlineStr">
         <is>
           <t>M06-F01</t>
         </is>
       </c>
-      <c r="B9" s="23" t="inlineStr">
+      <c r="B9" s="48" t="inlineStr">
         <is>
           <t>Report Creation</t>
         </is>
       </c>
-      <c r="C9" s="24">
-        <f>COUNTIFS('Module06'!$C$2:$C$32, A9, 'Module06'!$M$2:$M$32, "High")</f>
-        <v/>
-      </c>
-      <c r="D9" s="25">
-        <f>COUNTIFS('Module06'!$C$2:$C$32, A9, 'Module06'!$M$2:$M$32, "Medium")</f>
-        <v/>
-      </c>
-      <c r="E9" s="26">
-        <f>COUNTIFS('Module06'!$C$2:$C$32, A9, 'Module06'!$M$2:$M$32, "Low")</f>
-        <v/>
-      </c>
-      <c r="F9" s="27">
+      <c r="C9" s="49">
+        <f>COUNTIFS('Module06'!$C$2:$C$30, A9, 'Module06'!$M$2:$M$30, "High")</f>
+        <v/>
+      </c>
+      <c r="D9" s="50">
+        <f>COUNTIFS('Module06'!$C$2:$C$30, A9, 'Module06'!$M$2:$M$30, "Medium")</f>
+        <v/>
+      </c>
+      <c r="E9" s="51">
+        <f>COUNTIFS('Module06'!$C$2:$C$30, A9, 'Module06'!$M$2:$M$30, "Low")</f>
+        <v/>
+      </c>
+      <c r="F9" s="52">
         <f>SUM(C9:E9)</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="28" t="inlineStr">
+      <c r="A10" s="53" t="inlineStr">
         <is>
           <t>M06-F02</t>
         </is>
       </c>
-      <c r="B10" s="29" t="inlineStr">
+      <c r="B10" s="54" t="inlineStr">
         <is>
           <t>Draft Saving &amp; Editing</t>
         </is>
       </c>
-      <c r="C10" s="30">
-        <f>COUNTIFS('Module06'!$C$2:$C$32, A10, 'Module06'!$M$2:$M$32, "High")</f>
-        <v/>
-      </c>
-      <c r="D10" s="31">
-        <f>COUNTIFS('Module06'!$C$2:$C$32, A10, 'Module06'!$M$2:$M$32, "Medium")</f>
-        <v/>
-      </c>
-      <c r="E10" s="32">
-        <f>COUNTIFS('Module06'!$C$2:$C$32, A10, 'Module06'!$M$2:$M$32, "Low")</f>
-        <v/>
-      </c>
-      <c r="F10" s="33">
+      <c r="C10" s="55">
+        <f>COUNTIFS('Module06'!$C$2:$C$30, A10, 'Module06'!$M$2:$M$30, "High")</f>
+        <v/>
+      </c>
+      <c r="D10" s="56">
+        <f>COUNTIFS('Module06'!$C$2:$C$30, A10, 'Module06'!$M$2:$M$30, "Medium")</f>
+        <v/>
+      </c>
+      <c r="E10" s="57">
+        <f>COUNTIFS('Module06'!$C$2:$C$30, A10, 'Module06'!$M$2:$M$30, "Low")</f>
+        <v/>
+      </c>
+      <c r="F10" s="58">
         <f>SUM(C10:E10)</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="22" t="inlineStr">
+      <c r="A11" s="47" t="inlineStr">
         <is>
           <t>M06-F03</t>
         </is>
       </c>
-      <c r="B11" s="23" t="inlineStr">
+      <c r="B11" s="48" t="inlineStr">
         <is>
           <t>Automatic Date Calculation</t>
         </is>
       </c>
-      <c r="C11" s="24">
-        <f>COUNTIFS('Module06'!$C$2:$C$32, A11, 'Module06'!$M$2:$M$32, "High")</f>
-        <v/>
-      </c>
-      <c r="D11" s="25">
-        <f>COUNTIFS('Module06'!$C$2:$C$32, A11, 'Module06'!$M$2:$M$32, "Medium")</f>
-        <v/>
-      </c>
-      <c r="E11" s="26">
-        <f>COUNTIFS('Module06'!$C$2:$C$32, A11, 'Module06'!$M$2:$M$32, "Low")</f>
-        <v/>
-      </c>
-      <c r="F11" s="27">
+      <c r="C11" s="49">
+        <f>COUNTIFS('Module06'!$C$2:$C$30, A11, 'Module06'!$M$2:$M$30, "High")</f>
+        <v/>
+      </c>
+      <c r="D11" s="50">
+        <f>COUNTIFS('Module06'!$C$2:$C$30, A11, 'Module06'!$M$2:$M$30, "Medium")</f>
+        <v/>
+      </c>
+      <c r="E11" s="51">
+        <f>COUNTIFS('Module06'!$C$2:$C$30, A11, 'Module06'!$M$2:$M$30, "Low")</f>
+        <v/>
+      </c>
+      <c r="F11" s="52">
         <f>SUM(C11:E11)</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="28" t="inlineStr">
+      <c r="A12" s="53" t="inlineStr">
         <is>
           <t>M06-F04</t>
         </is>
       </c>
-      <c r="B12" s="29" t="inlineStr">
+      <c r="B12" s="54" t="inlineStr">
         <is>
           <t>Dynamic Task Table Management</t>
         </is>
       </c>
-      <c r="C12" s="30">
-        <f>COUNTIFS('Module06'!$C$2:$C$32, A12, 'Module06'!$M$2:$M$32, "High")</f>
-        <v/>
-      </c>
-      <c r="D12" s="31">
-        <f>COUNTIFS('Module06'!$C$2:$C$32, A12, 'Module06'!$M$2:$M$32, "Medium")</f>
-        <v/>
-      </c>
-      <c r="E12" s="32">
-        <f>COUNTIFS('Module06'!$C$2:$C$32, A12, 'Module06'!$M$2:$M$32, "Low")</f>
-        <v/>
-      </c>
-      <c r="F12" s="33">
+      <c r="C12" s="55">
+        <f>COUNTIFS('Module06'!$C$2:$C$30, A12, 'Module06'!$M$2:$M$30, "High")</f>
+        <v/>
+      </c>
+      <c r="D12" s="56">
+        <f>COUNTIFS('Module06'!$C$2:$C$30, A12, 'Module06'!$M$2:$M$30, "Medium")</f>
+        <v/>
+      </c>
+      <c r="E12" s="57">
+        <f>COUNTIFS('Module06'!$C$2:$C$30, A12, 'Module06'!$M$2:$M$30, "Low")</f>
+        <v/>
+      </c>
+      <c r="F12" s="58">
         <f>SUM(C12:E12)</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="22" t="inlineStr">
+      <c r="A13" s="47" t="inlineStr">
         <is>
           <t>M06-F05</t>
         </is>
       </c>
-      <c r="B13" s="23" t="inlineStr">
+      <c r="B13" s="48" t="inlineStr">
         <is>
           <t>Working Hours Calculation</t>
         </is>
       </c>
-      <c r="C13" s="24">
-        <f>COUNTIFS('Module06'!$C$2:$C$32, A13, 'Module06'!$M$2:$M$32, "High")</f>
-        <v/>
-      </c>
-      <c r="D13" s="25">
-        <f>COUNTIFS('Module06'!$C$2:$C$32, A13, 'Module06'!$M$2:$M$32, "Medium")</f>
-        <v/>
-      </c>
-      <c r="E13" s="26">
-        <f>COUNTIFS('Module06'!$C$2:$C$32, A13, 'Module06'!$M$2:$M$32, "Low")</f>
-        <v/>
-      </c>
-      <c r="F13" s="27">
+      <c r="C13" s="49">
+        <f>COUNTIFS('Module06'!$C$2:$C$30, A13, 'Module06'!$M$2:$M$30, "High")</f>
+        <v/>
+      </c>
+      <c r="D13" s="50">
+        <f>COUNTIFS('Module06'!$C$2:$C$30, A13, 'Module06'!$M$2:$M$30, "Medium")</f>
+        <v/>
+      </c>
+      <c r="E13" s="51">
+        <f>COUNTIFS('Module06'!$C$2:$C$30, A13, 'Module06'!$M$2:$M$30, "Low")</f>
+        <v/>
+      </c>
+      <c r="F13" s="52">
         <f>SUM(C13:E13)</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="28" t="inlineStr">
+      <c r="A14" s="53" t="inlineStr">
         <is>
           <t>M06-F06</t>
         </is>
       </c>
-      <c r="B14" s="29" t="inlineStr">
+      <c r="B14" s="54" t="inlineStr">
         <is>
           <t>Report Submission</t>
         </is>
       </c>
-      <c r="C14" s="30">
-        <f>COUNTIFS('Module06'!$C$2:$C$32, A14, 'Module06'!$M$2:$M$32, "High")</f>
-        <v/>
-      </c>
-      <c r="D14" s="31">
-        <f>COUNTIFS('Module06'!$C$2:$C$32, A14, 'Module06'!$M$2:$M$32, "Medium")</f>
-        <v/>
-      </c>
-      <c r="E14" s="32">
-        <f>COUNTIFS('Module06'!$C$2:$C$32, A14, 'Module06'!$M$2:$M$32, "Low")</f>
-        <v/>
-      </c>
-      <c r="F14" s="33">
+      <c r="C14" s="55">
+        <f>COUNTIFS('Module06'!$C$2:$C$30, A14, 'Module06'!$M$2:$M$30, "High")</f>
+        <v/>
+      </c>
+      <c r="D14" s="56">
+        <f>COUNTIFS('Module06'!$C$2:$C$30, A14, 'Module06'!$M$2:$M$30, "Medium")</f>
+        <v/>
+      </c>
+      <c r="E14" s="57">
+        <f>COUNTIFS('Module06'!$C$2:$C$30, A14, 'Module06'!$M$2:$M$30, "Low")</f>
+        <v/>
+      </c>
+      <c r="F14" s="58">
         <f>SUM(C14:E14)</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="22" t="inlineStr">
+      <c r="A15" s="47" t="inlineStr">
         <is>
           <t>M06-F07</t>
         </is>
       </c>
-      <c r="B15" s="23" t="inlineStr">
+      <c r="B15" s="48" t="inlineStr">
         <is>
           <t>Read-only Submitted Reports</t>
         </is>
       </c>
-      <c r="C15" s="24">
-        <f>COUNTIFS('Module06'!$C$2:$C$32, A15, 'Module06'!$M$2:$M$32, "High")</f>
-        <v/>
-      </c>
-      <c r="D15" s="25">
-        <f>COUNTIFS('Module06'!$C$2:$C$32, A15, 'Module06'!$M$2:$M$32, "Medium")</f>
-        <v/>
-      </c>
-      <c r="E15" s="26">
-        <f>COUNTIFS('Module06'!$C$2:$C$32, A15, 'Module06'!$M$2:$M$32, "Low")</f>
-        <v/>
-      </c>
-      <c r="F15" s="27">
+      <c r="C15" s="49">
+        <f>COUNTIFS('Module06'!$C$2:$C$30, A15, 'Module06'!$M$2:$M$30, "High")</f>
+        <v/>
+      </c>
+      <c r="D15" s="50">
+        <f>COUNTIFS('Module06'!$C$2:$C$30, A15, 'Module06'!$M$2:$M$30, "Medium")</f>
+        <v/>
+      </c>
+      <c r="E15" s="51">
+        <f>COUNTIFS('Module06'!$C$2:$C$30, A15, 'Module06'!$M$2:$M$30, "Low")</f>
+        <v/>
+      </c>
+      <c r="F15" s="52">
         <f>SUM(C15:E15)</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="28" t="inlineStr">
+      <c r="A16" s="53" t="inlineStr">
         <is>
           <t>M06-F08</t>
         </is>
       </c>
-      <c r="B16" s="29" t="inlineStr">
+      <c r="B16" s="54" t="inlineStr">
         <is>
           <t>Automated Email Notifications</t>
         </is>
       </c>
-      <c r="C16" s="30">
-        <f>COUNTIFS('Module06'!$C$2:$C$32, A16, 'Module06'!$M$2:$M$32, "High")</f>
-        <v/>
-      </c>
-      <c r="D16" s="31">
-        <f>COUNTIFS('Module06'!$C$2:$C$32, A16, 'Module06'!$M$2:$M$32, "Medium")</f>
-        <v/>
-      </c>
-      <c r="E16" s="32">
-        <f>COUNTIFS('Module06'!$C$2:$C$32, A16, 'Module06'!$M$2:$M$32, "Low")</f>
-        <v/>
-      </c>
-      <c r="F16" s="33">
+      <c r="C16" s="55">
+        <f>COUNTIFS('Module06'!$C$2:$C$30, A16, 'Module06'!$M$2:$M$30, "High")</f>
+        <v/>
+      </c>
+      <c r="D16" s="56">
+        <f>COUNTIFS('Module06'!$C$2:$C$30, A16, 'Module06'!$M$2:$M$30, "Medium")</f>
+        <v/>
+      </c>
+      <c r="E16" s="57">
+        <f>COUNTIFS('Module06'!$C$2:$C$30, A16, 'Module06'!$M$2:$M$30, "Low")</f>
+        <v/>
+      </c>
+      <c r="F16" s="58">
         <f>SUM(C16:E16)</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="22" t="inlineStr">
-        <is>
-          <t>M06-F09</t>
-        </is>
-      </c>
-      <c r="B17" s="23" t="inlineStr">
-        <is>
-          <t>Staff Report Viewing</t>
-        </is>
-      </c>
-      <c r="C17" s="24">
-        <f>COUNTIFS('Module06'!$C$2:$C$32, A17, 'Module06'!$M$2:$M$32, "High")</f>
-        <v/>
-      </c>
-      <c r="D17" s="25">
-        <f>COUNTIFS('Module06'!$C$2:$C$32, A17, 'Module06'!$M$2:$M$32, "Medium")</f>
-        <v/>
-      </c>
-      <c r="E17" s="26">
-        <f>COUNTIFS('Module06'!$C$2:$C$32, A17, 'Module06'!$M$2:$M$32, "Low")</f>
-        <v/>
-      </c>
-      <c r="F17" s="27">
-        <f>SUM(C17:E17)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="34" t="inlineStr">
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="59" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B18" s="35">
-        <f>COUNTA(A9:A17)&amp;" Features"</f>
-        <v/>
-      </c>
-      <c r="C18" s="34">
-        <f>SUM(C9:C17)</f>
-        <v/>
-      </c>
-      <c r="D18" s="34">
-        <f>SUM(D9:D17)</f>
-        <v/>
-      </c>
-      <c r="E18" s="34">
-        <f>SUM(E9:E17)</f>
-        <v/>
-      </c>
-      <c r="F18" s="34">
-        <f>SUM(F9:F17)</f>
+      <c r="B17" s="60">
+        <f>COUNTA(A9:A16)&amp;" Features"</f>
+        <v/>
+      </c>
+      <c r="C17" s="59">
+        <f>SUM(C9:C16)</f>
+        <v/>
+      </c>
+      <c r="D17" s="59">
+        <f>SUM(D9:D16)</f>
+        <v/>
+      </c>
+      <c r="E17" s="59">
+        <f>SUM(E9:E16)</f>
+        <v/>
+      </c>
+      <c r="F17" s="59">
+        <f>SUM(F9:F16)</f>
         <v/>
       </c>
     </row>
@@ -1288,26 +1489,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N32"/>
+  <dimension ref="A1:N30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="32" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="30" customWidth="1" min="7" max="7"/>
     <col width="28" customWidth="1" min="8" max="8"/>
-    <col width="48" customWidth="1" min="9" max="9"/>
-    <col width="48" customWidth="1" min="10" max="10"/>
+    <col width="48" customWidth="1" min="9" max="10"/>
     <col width="36" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="32" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
+    <row r="1" ht="27.95" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ID</t>
@@ -1435,10 +1634,14 @@
 System opens report submission interface with auto-filled student profile info.</t>
         </is>
       </c>
-      <c r="K2" s="4" t="inlineStr"/>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>Create Internship Report button was displayed. System opened report submission interface with auto-filled student profile info as expected.</t>
+        </is>
+      </c>
       <c r="L2" s="5" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M2" s="6" t="inlineStr">
@@ -1507,10 +1710,14 @@
 Student cannot open report creation interface.</t>
         </is>
       </c>
-      <c r="K3" s="9" t="inlineStr"/>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>Create Internship Report button was hidden for student in completed group. Student could not open creation interface.</t>
+        </is>
+      </c>
       <c r="L3" s="5" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M3" s="6" t="inlineStr">
@@ -1579,10 +1786,14 @@
 Student cannot open report creation interface.</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr"/>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>Create Internship Report button was hidden for student in archived group. Student could not open creation interface.</t>
+        </is>
+      </c>
       <c r="L4" s="5" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M4" s="6" t="inlineStr">
@@ -1649,10 +1860,14 @@
           <t>Create Internship Report button is not present for Staff account.</t>
         </is>
       </c>
-      <c r="K5" s="9" t="inlineStr"/>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>Create Internship Report button was not present when logged in with Staff account.</t>
+        </is>
+      </c>
       <c r="L5" s="5" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M5" s="6" t="inlineStr">
@@ -1722,10 +1937,14 @@
 Data is saved to database without triggering submit validation.</t>
         </is>
       </c>
-      <c r="K6" s="4" t="inlineStr"/>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>Report was saved with status Draft. Success message "Draft saved successfully" appeared and data was saved without triggering submit validation.</t>
+        </is>
+      </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M6" s="6" t="inlineStr">
@@ -1795,10 +2014,14 @@
 Report status remains Draft.</t>
         </is>
       </c>
-      <c r="K7" s="9" t="inlineStr"/>
+      <c r="K7" s="9" t="inlineStr">
+        <is>
+          <t>Draft report updated successfully upon multiple edits without restriction. Report status remained Draft.</t>
+        </is>
+      </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M7" s="6" t="inlineStr">
@@ -1867,10 +2090,14 @@
 Draft report is hidden from Staff view.</t>
         </is>
       </c>
-      <c r="K8" s="4" t="inlineStr"/>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>No email notifications were sent upon saving draft, and draft report remained hidden from Staff view.</t>
+        </is>
+      </c>
       <c r="L8" s="5" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M8" s="6" t="inlineStr">
@@ -1938,10 +2165,14 @@
 End Date field is read-only.</t>
         </is>
       </c>
-      <c r="K9" s="9" t="inlineStr"/>
+      <c r="K9" s="9" t="inlineStr">
+        <is>
+          <t>End Date field automatically filled with "2026-08-16" (Sunday, +13 days) and remained read-only.</t>
+        </is>
+      </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M9" s="6" t="inlineStr">
@@ -2009,10 +2240,14 @@
 Action is blocked.</t>
         </is>
       </c>
-      <c r="K10" s="4" t="inlineStr"/>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>System displayed validation error "Start Date must be a Monday." and blocked action.</t>
+        </is>
+      </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M10" s="6" t="inlineStr">
@@ -2080,10 +2315,14 @@
 Action is blocked.</t>
         </is>
       </c>
-      <c r="K11" s="9" t="inlineStr"/>
+      <c r="K11" s="9" t="inlineStr">
+        <is>
+          <t>System displayed validation error "Start Date must fall within the internship group period." and blocked action.</t>
+        </is>
+      </c>
       <c r="L11" s="5" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M11" s="6" t="inlineStr">
@@ -2152,10 +2391,14 @@
 Clicking Remove deletes row 2 cleanly.</t>
         </is>
       </c>
-      <c r="K12" s="4" t="inlineStr"/>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>Clicking Add Task Row appended a new empty task row. Clicking Remove deleted row cleanly.</t>
+        </is>
+      </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M12" s="6" t="inlineStr">
@@ -2223,10 +2466,14 @@
 Validation error message appears: "At least one task is required."</t>
         </is>
       </c>
-      <c r="K13" s="9" t="inlineStr"/>
+      <c r="K13" s="9" t="inlineStr">
+        <is>
+          <t>System blocked submission and displayed validation error "At least one task is required."</t>
+        </is>
+      </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M13" s="6" t="inlineStr">
@@ -2295,10 +2542,14 @@
 Validation error message appears highlighting required fields in task table.</t>
         </is>
       </c>
-      <c r="K14" s="4" t="inlineStr"/>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>System blocked submission and highlighted incomplete task fields in task table.</t>
+        </is>
+      </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M14" s="6" t="inlineStr">
@@ -2366,10 +2617,14 @@
 Total Bi-Weekly Hours automatically calculates to 80 hours.</t>
         </is>
       </c>
-      <c r="K15" s="9" t="inlineStr"/>
+      <c r="K15" s="9" t="inlineStr">
+        <is>
+          <t>Daily totals summed correctly and Total Bi-Weekly Hours automatically calculated to 80 hours.</t>
+        </is>
+      </c>
       <c r="L15" s="5" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M15" s="6" t="inlineStr">
@@ -2436,10 +2691,14 @@
 Error appears: "Working hours cannot be negative."</t>
         </is>
       </c>
-      <c r="K16" s="4" t="inlineStr"/>
-      <c r="L16" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>System allowed entering negative working hours (&lt; 0), allowed submitting the report, and sent email notifications without triggering validation errors.</t>
+        </is>
+      </c>
+      <c r="L16" s="6" t="inlineStr">
+        <is>
+          <t>Failed</t>
         </is>
       </c>
       <c r="M16" s="6" t="inlineStr">
@@ -2453,7 +2712,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="60" customHeight="1">
+    <row r="17" ht="75" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
           <t>TC-M06-016</t>
@@ -2506,10 +2765,14 @@
 Error appears: "Daily working hours cannot exceed 24 hours."</t>
         </is>
       </c>
-      <c r="K17" s="9" t="inlineStr"/>
-      <c r="L17" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K17" s="9" t="inlineStr">
+        <is>
+          <t>System allowed entering working hours exceeding 24 hours a day (&gt; 24), allowed submitting the report, and sent email notifications without triggering validation errors.</t>
+        </is>
+      </c>
+      <c r="L17" s="6" t="inlineStr">
+        <is>
+          <t>Failed</t>
         </is>
       </c>
       <c r="M17" s="6" t="inlineStr">
@@ -2574,10 +2837,14 @@
           <t>Non-numeric input is prevented or validation error appears: "Please enter a valid number."</t>
         </is>
       </c>
-      <c r="K18" s="4" t="inlineStr"/>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>Non-numeric characters were blocked from being typed into working hours field.</t>
+        </is>
+      </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M18" s="10" t="inlineStr">
@@ -2651,10 +2918,14 @@
 Success notification appears and page transitions to View mode.</t>
         </is>
       </c>
-      <c r="K19" s="9" t="inlineStr"/>
+      <c r="K19" s="9" t="inlineStr">
+        <is>
+          <t>Report was submitted successfully, status updated to Submitted, success message appeared, and form switched to View mode.</t>
+        </is>
+      </c>
       <c r="L19" s="5" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M19" s="6" t="inlineStr">
@@ -2721,10 +2992,14 @@
 Validation error message appears: "Company Supervisor Name is required."</t>
         </is>
       </c>
-      <c r="K20" s="4" t="inlineStr"/>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>System blocked submission and displayed validation error "Company Supervisor Name is required."</t>
+        </is>
+      </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M20" s="6" t="inlineStr">
@@ -2791,10 +3066,14 @@
 Validation error message appears: "PNV Supervisor Email is required."</t>
         </is>
       </c>
-      <c r="K21" s="9" t="inlineStr"/>
+      <c r="K21" s="9" t="inlineStr">
+        <is>
+          <t>System blocked submission and displayed validation error "PNV Supervisor Email is required."</t>
+        </is>
+      </c>
       <c r="L21" s="5" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M21" s="6" t="inlineStr">
@@ -2861,10 +3140,14 @@
 Validation error message appears: "Invalid email address format."</t>
         </is>
       </c>
-      <c r="K22" s="4" t="inlineStr"/>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>System blocked submission and displayed validation error "Invalid email address format."</t>
+        </is>
+      </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M22" s="6" t="inlineStr">
@@ -2931,10 +3214,14 @@
 Validation error message appears: "Company Supervisor Email is required."</t>
         </is>
       </c>
-      <c r="K23" s="9" t="inlineStr"/>
+      <c r="K23" s="9" t="inlineStr">
+        <is>
+          <t>System blocked submission and displayed validation error "Company Supervisor Email is required."</t>
+        </is>
+      </c>
       <c r="L23" s="5" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M23" s="6" t="inlineStr">
@@ -3001,10 +3288,14 @@
 Validation error message appears: "Invalid email address format."</t>
         </is>
       </c>
-      <c r="K24" s="4" t="inlineStr"/>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>System blocked submission and displayed validation error "Invalid email address format."</t>
+        </is>
+      </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M24" s="6" t="inlineStr">
@@ -3071,10 +3362,14 @@
 Validation error message appears: "Challenges field is required."</t>
         </is>
       </c>
-      <c r="K25" s="9" t="inlineStr"/>
+      <c r="K25" s="9" t="inlineStr">
+        <is>
+          <t>System blocked submission and displayed validation error "Challenges field is required."</t>
+        </is>
+      </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M25" s="6" t="inlineStr">
@@ -3141,10 +3436,14 @@
 Validation error message appears: "Support Needed field is required."</t>
         </is>
       </c>
-      <c r="K26" s="4" t="inlineStr"/>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>System blocked submission and displayed validation error "Support Needed field is required."</t>
+        </is>
+      </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M26" s="6" t="inlineStr">
@@ -3212,10 +3511,14 @@
 Report is not submitted and remains in edit form.</t>
         </is>
       </c>
-      <c r="K27" s="9" t="inlineStr"/>
+      <c r="K27" s="9" t="inlineStr">
+        <is>
+          <t>Confirmation popup closed upon clicking Cancel, report was not submitted, and form remained in edit mode.</t>
+        </is>
+      </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M27" s="10" t="inlineStr">
@@ -3284,10 +3587,14 @@
 Student cannot modify content.</t>
         </is>
       </c>
-      <c r="K28" s="4" t="inlineStr"/>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>Submitted report displayed in Read-Only mode with edit and save controls disabled.</t>
+        </is>
+      </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M28" s="6" t="inlineStr">
@@ -3354,10 +3661,14 @@
           <t>Automated email notification is delivered to both supervisor email addresses containing report summary.</t>
         </is>
       </c>
-      <c r="K29" s="9" t="inlineStr"/>
+      <c r="K29" s="9" t="inlineStr">
+        <is>
+          <t>Automated email notifications containing report summary were delivered to both PNV and Company supervisors upon submission.</t>
+        </is>
+      </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M29" s="6" t="inlineStr">
@@ -3425,10 +3736,14 @@
 Warning message appears notifying student that email delivery failed, and error is logged.</t>
         </is>
       </c>
-      <c r="K30" s="4" t="inlineStr"/>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>Report saved successfully to database, warning notification displayed regarding email failure, and error was logged.</t>
+        </is>
+      </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>Not Run</t>
+          <t>Passed</t>
         </is>
       </c>
       <c r="M30" s="10" t="inlineStr">
@@ -3442,155 +3757,13 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="75" customHeight="1">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>TC-M06-030</t>
-        </is>
-      </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>Module 06 - Bi-Weekly Internship Reports</t>
-        </is>
-      </c>
-      <c r="C31" s="8" t="inlineStr">
-        <is>
-          <t>M06-F09</t>
-        </is>
-      </c>
-      <c r="D31" s="9" t="inlineStr">
-        <is>
-          <t>Staff Report Viewing</t>
-        </is>
-      </c>
-      <c r="E31" s="9" t="inlineStr">
-        <is>
-          <t>Staff View Student Internship Report</t>
-        </is>
-      </c>
-      <c r="F31" s="9" t="inlineStr">
-        <is>
-          <t>Verify Staff can view submitted bi-weekly internship reports of students.</t>
-        </is>
-      </c>
-      <c r="G31" s="9" t="inlineStr">
-        <is>
-          <t>User is logged in as Staff.
-Student has submitted a bi-weekly report.</t>
-        </is>
-      </c>
-      <c r="H31" s="9" t="inlineStr">
-        <is>
-          <t>StaffEmail="staff@passerellesnumeriques.org"</t>
-        </is>
-      </c>
-      <c r="I31" s="9" t="inlineStr">
-        <is>
-          <t>1. Access Internship Management interface;
-2. Select student report list;
-3. Click View on student's submitted report.</t>
-        </is>
-      </c>
-      <c r="J31" s="9" t="inlineStr">
-        <is>
-          <t>Staff can view complete report content (tasks, hours, challenges, supervisor info) in Read-Only mode.</t>
-        </is>
-      </c>
-      <c r="K31" s="9" t="inlineStr"/>
-      <c r="L31" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M31" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="N31" s="9" t="inlineStr">
-        <is>
-          <t>Related Requirement: M06-F09, Business Rules 6.8</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="60" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>TC-M06-031</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>Module 06 - Bi-Weekly Internship Reports</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>M06-F09</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>Staff Report Viewing</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>Staff Cannot Edit or Delete Student Report</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>Verify Staff users cannot modify or delete submitted student reports.</t>
-        </is>
-      </c>
-      <c r="G32" s="4" t="inlineStr">
-        <is>
-          <t>User is logged in as Staff.
-Viewing submitted student report.</t>
-        </is>
-      </c>
-      <c r="H32" s="4" t="inlineStr">
-        <is>
-          <t>StaffEmail="staff@passerellesnumeriques.org"</t>
-        </is>
-      </c>
-      <c r="I32" s="4" t="inlineStr">
-        <is>
-          <t>1. Open student submitted report;
-2. Check for edit/delete controls.</t>
-        </is>
-      </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>No edit or delete buttons are available for Staff.
-Report content is strictly Read-Only.</t>
-        </is>
-      </c>
-      <c r="K32" s="4" t="inlineStr"/>
-      <c r="L32" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M32" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="N32" s="4" t="inlineStr">
-        <is>
-          <t>Related Requirement: M06-F09, Business Rules 6.8</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:N32"/>
+  <autoFilter ref="A1:N30"/>
   <dataValidations count="2">
-    <dataValidation sqref="L2:L132" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Please select a valid state: Passed, Failed, or Not Run" type="list">
+    <dataValidation sqref="L2:L130" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Please select a valid state: Passed, Failed, or Not Run" type="list">
       <formula1>"Passed,Failed,Not Run"</formula1>
     </dataValidation>
-    <dataValidation sqref="M2:M132" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Priority" error="Please select a valid priority: High, Medium, or Low" type="list">
+    <dataValidation sqref="M2:M130" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Priority" error="Please select a valid priority: High, Medium, or Low" type="list">
       <formula1>"High,Medium,Low"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Tests/excel/module06_test_cases.xlsx
+++ b/Tests/excel/module06_test_cases.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Report" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Module06" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Module06" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Module06'!$A$1:$N$32</definedName>
@@ -398,14 +398,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -429,10 +429,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="FF0000"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -456,10 +456,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="FFFF00"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -483,10 +483,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="00FF00"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -515,8 +515,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -542,8 +542,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -569,7 +569,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>7</col>
@@ -584,9 +584,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>

--- a/Tests/excel/module06_test_cases.xlsx
+++ b/Tests/excel/module06_test_cases.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Module06" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Module06'!$A$1:$N$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Module06'!$A$1:$P$32</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="18">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -48,7 +48,7 @@
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
-      <color rgb="0064748B"/>
+      <color rgb="00137333"/>
       <sz val="10"/>
     </font>
     <font>
@@ -73,12 +73,6 @@
       <name val="Segoe UI"/>
       <i val="1"/>
       <color rgb="00555555"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <b val="1"/>
-      <color rgb="00137333"/>
       <sz val="10"/>
     </font>
     <font>
@@ -145,8 +139,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F1F5F9"/>
-        <bgColor rgb="00F1F5F9"/>
+        <fgColor rgb="00E6F4EA"/>
+        <bgColor rgb="00E6F4EA"/>
       </patternFill>
     </fill>
     <fill>
@@ -175,8 +169,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E6F4EA"/>
-        <bgColor rgb="00E6F4EA"/>
+        <fgColor rgb="00F1F5F9"/>
+        <bgColor rgb="00F1F5F9"/>
       </patternFill>
     </fill>
   </fills>
@@ -254,25 +248,25 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -291,7 +285,7 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -309,16 +303,16 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1009,15 +1003,15 @@
         </is>
       </c>
       <c r="C9" s="24">
-        <f>COUNTIFS('Module06'!$C$2:$C$32, A9, 'Module06'!$M$2:$M$32, "High")</f>
+        <f>COUNTIFS('Module06'!$C$2:$C$32, A9, 'Module06'!$O$2:$O$32, "High")</f>
         <v/>
       </c>
       <c r="D9" s="25">
-        <f>COUNTIFS('Module06'!$C$2:$C$32, A9, 'Module06'!$M$2:$M$32, "Medium")</f>
+        <f>COUNTIFS('Module06'!$C$2:$C$32, A9, 'Module06'!$O$2:$O$32, "Medium")</f>
         <v/>
       </c>
       <c r="E9" s="26">
-        <f>COUNTIFS('Module06'!$C$2:$C$32, A9, 'Module06'!$M$2:$M$32, "Low")</f>
+        <f>COUNTIFS('Module06'!$C$2:$C$32, A9, 'Module06'!$O$2:$O$32, "Low")</f>
         <v/>
       </c>
       <c r="F9" s="27">
@@ -1037,15 +1031,15 @@
         </is>
       </c>
       <c r="C10" s="30">
-        <f>COUNTIFS('Module06'!$C$2:$C$32, A10, 'Module06'!$M$2:$M$32, "High")</f>
+        <f>COUNTIFS('Module06'!$C$2:$C$32, A10, 'Module06'!$O$2:$O$32, "High")</f>
         <v/>
       </c>
       <c r="D10" s="31">
-        <f>COUNTIFS('Module06'!$C$2:$C$32, A10, 'Module06'!$M$2:$M$32, "Medium")</f>
+        <f>COUNTIFS('Module06'!$C$2:$C$32, A10, 'Module06'!$O$2:$O$32, "Medium")</f>
         <v/>
       </c>
       <c r="E10" s="32">
-        <f>COUNTIFS('Module06'!$C$2:$C$32, A10, 'Module06'!$M$2:$M$32, "Low")</f>
+        <f>COUNTIFS('Module06'!$C$2:$C$32, A10, 'Module06'!$O$2:$O$32, "Low")</f>
         <v/>
       </c>
       <c r="F10" s="33">
@@ -1065,15 +1059,15 @@
         </is>
       </c>
       <c r="C11" s="24">
-        <f>COUNTIFS('Module06'!$C$2:$C$32, A11, 'Module06'!$M$2:$M$32, "High")</f>
+        <f>COUNTIFS('Module06'!$C$2:$C$32, A11, 'Module06'!$O$2:$O$32, "High")</f>
         <v/>
       </c>
       <c r="D11" s="25">
-        <f>COUNTIFS('Module06'!$C$2:$C$32, A11, 'Module06'!$M$2:$M$32, "Medium")</f>
+        <f>COUNTIFS('Module06'!$C$2:$C$32, A11, 'Module06'!$O$2:$O$32, "Medium")</f>
         <v/>
       </c>
       <c r="E11" s="26">
-        <f>COUNTIFS('Module06'!$C$2:$C$32, A11, 'Module06'!$M$2:$M$32, "Low")</f>
+        <f>COUNTIFS('Module06'!$C$2:$C$32, A11, 'Module06'!$O$2:$O$32, "Low")</f>
         <v/>
       </c>
       <c r="F11" s="27">
@@ -1093,15 +1087,15 @@
         </is>
       </c>
       <c r="C12" s="30">
-        <f>COUNTIFS('Module06'!$C$2:$C$32, A12, 'Module06'!$M$2:$M$32, "High")</f>
+        <f>COUNTIFS('Module06'!$C$2:$C$32, A12, 'Module06'!$O$2:$O$32, "High")</f>
         <v/>
       </c>
       <c r="D12" s="31">
-        <f>COUNTIFS('Module06'!$C$2:$C$32, A12, 'Module06'!$M$2:$M$32, "Medium")</f>
+        <f>COUNTIFS('Module06'!$C$2:$C$32, A12, 'Module06'!$O$2:$O$32, "Medium")</f>
         <v/>
       </c>
       <c r="E12" s="32">
-        <f>COUNTIFS('Module06'!$C$2:$C$32, A12, 'Module06'!$M$2:$M$32, "Low")</f>
+        <f>COUNTIFS('Module06'!$C$2:$C$32, A12, 'Module06'!$O$2:$O$32, "Low")</f>
         <v/>
       </c>
       <c r="F12" s="33">
@@ -1121,15 +1115,15 @@
         </is>
       </c>
       <c r="C13" s="24">
-        <f>COUNTIFS('Module06'!$C$2:$C$32, A13, 'Module06'!$M$2:$M$32, "High")</f>
+        <f>COUNTIFS('Module06'!$C$2:$C$32, A13, 'Module06'!$O$2:$O$32, "High")</f>
         <v/>
       </c>
       <c r="D13" s="25">
-        <f>COUNTIFS('Module06'!$C$2:$C$32, A13, 'Module06'!$M$2:$M$32, "Medium")</f>
+        <f>COUNTIFS('Module06'!$C$2:$C$32, A13, 'Module06'!$O$2:$O$32, "Medium")</f>
         <v/>
       </c>
       <c r="E13" s="26">
-        <f>COUNTIFS('Module06'!$C$2:$C$32, A13, 'Module06'!$M$2:$M$32, "Low")</f>
+        <f>COUNTIFS('Module06'!$C$2:$C$32, A13, 'Module06'!$O$2:$O$32, "Low")</f>
         <v/>
       </c>
       <c r="F13" s="27">
@@ -1149,15 +1143,15 @@
         </is>
       </c>
       <c r="C14" s="30">
-        <f>COUNTIFS('Module06'!$C$2:$C$32, A14, 'Module06'!$M$2:$M$32, "High")</f>
+        <f>COUNTIFS('Module06'!$C$2:$C$32, A14, 'Module06'!$O$2:$O$32, "High")</f>
         <v/>
       </c>
       <c r="D14" s="31">
-        <f>COUNTIFS('Module06'!$C$2:$C$32, A14, 'Module06'!$M$2:$M$32, "Medium")</f>
+        <f>COUNTIFS('Module06'!$C$2:$C$32, A14, 'Module06'!$O$2:$O$32, "Medium")</f>
         <v/>
       </c>
       <c r="E14" s="32">
-        <f>COUNTIFS('Module06'!$C$2:$C$32, A14, 'Module06'!$M$2:$M$32, "Low")</f>
+        <f>COUNTIFS('Module06'!$C$2:$C$32, A14, 'Module06'!$O$2:$O$32, "Low")</f>
         <v/>
       </c>
       <c r="F14" s="33">
@@ -1177,15 +1171,15 @@
         </is>
       </c>
       <c r="C15" s="24">
-        <f>COUNTIFS('Module06'!$C$2:$C$32, A15, 'Module06'!$M$2:$M$32, "High")</f>
+        <f>COUNTIFS('Module06'!$C$2:$C$32, A15, 'Module06'!$O$2:$O$32, "High")</f>
         <v/>
       </c>
       <c r="D15" s="25">
-        <f>COUNTIFS('Module06'!$C$2:$C$32, A15, 'Module06'!$M$2:$M$32, "Medium")</f>
+        <f>COUNTIFS('Module06'!$C$2:$C$32, A15, 'Module06'!$O$2:$O$32, "Medium")</f>
         <v/>
       </c>
       <c r="E15" s="26">
-        <f>COUNTIFS('Module06'!$C$2:$C$32, A15, 'Module06'!$M$2:$M$32, "Low")</f>
+        <f>COUNTIFS('Module06'!$C$2:$C$32, A15, 'Module06'!$O$2:$O$32, "Low")</f>
         <v/>
       </c>
       <c r="F15" s="27">
@@ -1205,15 +1199,15 @@
         </is>
       </c>
       <c r="C16" s="30">
-        <f>COUNTIFS('Module06'!$C$2:$C$32, A16, 'Module06'!$M$2:$M$32, "High")</f>
+        <f>COUNTIFS('Module06'!$C$2:$C$32, A16, 'Module06'!$O$2:$O$32, "High")</f>
         <v/>
       </c>
       <c r="D16" s="31">
-        <f>COUNTIFS('Module06'!$C$2:$C$32, A16, 'Module06'!$M$2:$M$32, "Medium")</f>
+        <f>COUNTIFS('Module06'!$C$2:$C$32, A16, 'Module06'!$O$2:$O$32, "Medium")</f>
         <v/>
       </c>
       <c r="E16" s="32">
-        <f>COUNTIFS('Module06'!$C$2:$C$32, A16, 'Module06'!$M$2:$M$32, "Low")</f>
+        <f>COUNTIFS('Module06'!$C$2:$C$32, A16, 'Module06'!$O$2:$O$32, "Low")</f>
         <v/>
       </c>
       <c r="F16" s="33">
@@ -1233,15 +1227,15 @@
         </is>
       </c>
       <c r="C17" s="24">
-        <f>COUNTIFS('Module06'!$C$2:$C$32, A17, 'Module06'!$M$2:$M$32, "High")</f>
+        <f>COUNTIFS('Module06'!$C$2:$C$32, A17, 'Module06'!$O$2:$O$32, "High")</f>
         <v/>
       </c>
       <c r="D17" s="25">
-        <f>COUNTIFS('Module06'!$C$2:$C$32, A17, 'Module06'!$M$2:$M$32, "Medium")</f>
+        <f>COUNTIFS('Module06'!$C$2:$C$32, A17, 'Module06'!$O$2:$O$32, "Medium")</f>
         <v/>
       </c>
       <c r="E17" s="26">
-        <f>COUNTIFS('Module06'!$C$2:$C$32, A17, 'Module06'!$M$2:$M$32, "Low")</f>
+        <f>COUNTIFS('Module06'!$C$2:$C$32, A17, 'Module06'!$O$2:$O$32, "Low")</f>
         <v/>
       </c>
       <c r="F17" s="27">
@@ -1288,7 +1282,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N32"/>
+  <dimension ref="A1:P32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1301,10 +1295,12 @@
     <col width="28" customWidth="1" min="8" max="8"/>
     <col width="48" customWidth="1" min="9" max="9"/>
     <col width="48" customWidth="1" min="10" max="10"/>
-    <col width="36" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="32" customWidth="1" min="14" max="14"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
+    <col width="36" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="25" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="32" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -1360,20 +1356,30 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>Evidence</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Evidence</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -1435,18 +1441,24 @@
 System opens report submission interface with auto-filled student profile info.</t>
         </is>
       </c>
-      <c r="K2" s="4" t="inlineStr"/>
-      <c r="L2" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M2" s="6" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="4" t="inlineStr">
+        <is>
+          <t>Create Internship Report button was displayed. System opened report submission interface with auto-filled student profile info as expected.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr"/>
+      <c r="O2" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N2" s="4" t="inlineStr">
+      <c r="P2" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M06-F01, Business Rules 6.1</t>
         </is>
@@ -1507,18 +1519,24 @@
 Student cannot open report creation interface.</t>
         </is>
       </c>
-      <c r="K3" s="9" t="inlineStr"/>
-      <c r="L3" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M3" s="6" t="inlineStr">
+      <c r="K3" s="7" t="inlineStr"/>
+      <c r="L3" s="9" t="inlineStr">
+        <is>
+          <t>Create Internship Report button was hidden for student in completed group. Student could not open creation interface.</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="N3" s="7" t="inlineStr"/>
+      <c r="O3" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N3" s="9" t="inlineStr">
+      <c r="P3" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M06-F01, Business Rules 6.1</t>
         </is>
@@ -1579,18 +1597,24 @@
 Student cannot open report creation interface.</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr"/>
-      <c r="L4" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M4" s="6" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>Create Internship Report button was hidden for student in archived group. Student could not open creation interface.</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr"/>
+      <c r="O4" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="P4" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M06-F01, Business Rules 6.1</t>
         </is>
@@ -1649,18 +1673,24 @@
           <t>Create Internship Report button is not present for Staff account.</t>
         </is>
       </c>
-      <c r="K5" s="9" t="inlineStr"/>
-      <c r="L5" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M5" s="6" t="inlineStr">
+      <c r="K5" s="7" t="inlineStr"/>
+      <c r="L5" s="9" t="inlineStr">
+        <is>
+          <t>Create Internship Report button was not present when logged in with Staff account.</t>
+        </is>
+      </c>
+      <c r="M5" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="N5" s="7" t="inlineStr"/>
+      <c r="O5" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N5" s="9" t="inlineStr">
+      <c r="P5" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M06-F01, Business Rules 6.1</t>
         </is>
@@ -1722,18 +1752,24 @@
 Data is saved to database without triggering submit validation.</t>
         </is>
       </c>
-      <c r="K6" s="4" t="inlineStr"/>
-      <c r="L6" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M6" s="6" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>Report was saved with status Draft. Success message "Draft saved successfully" appeared and data was saved without triggering submit validation.</t>
+        </is>
+      </c>
+      <c r="M6" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr"/>
+      <c r="O6" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N6" s="4" t="inlineStr">
+      <c r="P6" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M06-F02, Business Rules 6.2</t>
         </is>
@@ -1795,18 +1831,24 @@
 Report status remains Draft.</t>
         </is>
       </c>
-      <c r="K7" s="9" t="inlineStr"/>
-      <c r="L7" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M7" s="6" t="inlineStr">
+      <c r="K7" s="7" t="inlineStr"/>
+      <c r="L7" s="9" t="inlineStr">
+        <is>
+          <t>Draft report updated successfully upon multiple edits without restriction. Report status remained Draft.</t>
+        </is>
+      </c>
+      <c r="M7" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="N7" s="7" t="inlineStr"/>
+      <c r="O7" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N7" s="9" t="inlineStr">
+      <c r="P7" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M06-F02, Business Rules 6.2</t>
         </is>
@@ -1867,18 +1909,24 @@
 Draft report is hidden from Staff view.</t>
         </is>
       </c>
-      <c r="K8" s="4" t="inlineStr"/>
-      <c r="L8" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M8" s="6" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>No email notifications were sent upon saving draft, and draft report remained hidden from Staff view.</t>
+        </is>
+      </c>
+      <c r="M8" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr"/>
+      <c r="O8" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N8" s="4" t="inlineStr">
+      <c r="P8" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M06-F02, Business Rules 6.2</t>
         </is>
@@ -1938,18 +1986,24 @@
 End Date field is read-only.</t>
         </is>
       </c>
-      <c r="K9" s="9" t="inlineStr"/>
-      <c r="L9" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M9" s="6" t="inlineStr">
+      <c r="K9" s="7" t="inlineStr"/>
+      <c r="L9" s="9" t="inlineStr">
+        <is>
+          <t>End Date field automatically filled with "2026-08-16" (Sunday, +13 days) and remained read-only.</t>
+        </is>
+      </c>
+      <c r="M9" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="N9" s="7" t="inlineStr"/>
+      <c r="O9" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N9" s="9" t="inlineStr">
+      <c r="P9" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M06-F03, Business Rules 6.3</t>
         </is>
@@ -2009,18 +2063,24 @@
 Action is blocked.</t>
         </is>
       </c>
-      <c r="K10" s="4" t="inlineStr"/>
-      <c r="L10" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M10" s="6" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>System displayed validation error "Start Date must be a Monday." and blocked action.</t>
+        </is>
+      </c>
+      <c r="M10" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr"/>
+      <c r="O10" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N10" s="4" t="inlineStr">
+      <c r="P10" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M06-F03, Business Rules 6.3, Validation Rules (Section 8)</t>
         </is>
@@ -2080,18 +2140,24 @@
 Action is blocked.</t>
         </is>
       </c>
-      <c r="K11" s="9" t="inlineStr"/>
-      <c r="L11" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M11" s="6" t="inlineStr">
+      <c r="K11" s="7" t="inlineStr"/>
+      <c r="L11" s="9" t="inlineStr">
+        <is>
+          <t>System displayed validation error "Start Date must fall within the internship group period." and blocked action.</t>
+        </is>
+      </c>
+      <c r="M11" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="N11" s="7" t="inlineStr"/>
+      <c r="O11" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N11" s="9" t="inlineStr">
+      <c r="P11" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M06-F03, Business Rules 6.3, Validation Rules (Section 8)</t>
         </is>
@@ -2152,18 +2218,24 @@
 Clicking Remove deletes row 2 cleanly.</t>
         </is>
       </c>
-      <c r="K12" s="4" t="inlineStr"/>
-      <c r="L12" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M12" s="6" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>Clicking Add Task Row appended a new empty task row. Clicking Remove deleted row cleanly.</t>
+        </is>
+      </c>
+      <c r="M12" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr"/>
+      <c r="O12" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N12" s="4" t="inlineStr">
+      <c r="P12" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M06-F04, UI Standards</t>
         </is>
@@ -2223,18 +2295,24 @@
 Validation error message appears: "At least one task is required."</t>
         </is>
       </c>
-      <c r="K13" s="9" t="inlineStr"/>
-      <c r="L13" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M13" s="6" t="inlineStr">
+      <c r="K13" s="7" t="inlineStr"/>
+      <c r="L13" s="9" t="inlineStr">
+        <is>
+          <t>System blocked submission and displayed validation error "At least one task is required."</t>
+        </is>
+      </c>
+      <c r="M13" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="N13" s="7" t="inlineStr"/>
+      <c r="O13" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N13" s="9" t="inlineStr">
+      <c r="P13" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M06-F04, Validation Rules (Section 8)</t>
         </is>
@@ -2295,18 +2373,24 @@
 Validation error message appears highlighting required fields in task table.</t>
         </is>
       </c>
-      <c r="K14" s="4" t="inlineStr"/>
-      <c r="L14" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M14" s="6" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="4" t="inlineStr">
+        <is>
+          <t>System blocked submission and highlighted incomplete task fields in task table.</t>
+        </is>
+      </c>
+      <c r="M14" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr"/>
+      <c r="O14" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N14" s="4" t="inlineStr">
+      <c r="P14" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M06-F04, Validation Rules (Section 8)</t>
         </is>
@@ -2366,18 +2450,24 @@
 Total Bi-Weekly Hours automatically calculates to 80 hours.</t>
         </is>
       </c>
-      <c r="K15" s="9" t="inlineStr"/>
-      <c r="L15" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M15" s="6" t="inlineStr">
+      <c r="K15" s="7" t="inlineStr"/>
+      <c r="L15" s="9" t="inlineStr">
+        <is>
+          <t>Daily totals summed correctly and Total Bi-Weekly Hours automatically calculated to 80 hours.</t>
+        </is>
+      </c>
+      <c r="M15" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="N15" s="7" t="inlineStr"/>
+      <c r="O15" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N15" s="9" t="inlineStr">
+      <c r="P15" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M06-F05, Business Rules 6.4</t>
         </is>
@@ -2436,24 +2526,30 @@
 Error appears: "Working hours cannot be negative."</t>
         </is>
       </c>
-      <c r="K16" s="4" t="inlineStr"/>
-      <c r="L16" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="4" t="inlineStr">
+        <is>
+          <t>System allowed entering negative working hours (&lt; 0), allowed submitting the report, and sent email notifications without triggering validation errors.</t>
         </is>
       </c>
       <c r="M16" s="6" t="inlineStr">
         <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr"/>
+      <c r="O16" s="6" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N16" s="4" t="inlineStr">
+      <c r="P16" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M06-F05, Validation Rules (Section 8)</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="60" customHeight="1">
+    <row r="17" ht="75" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
           <t>TC-M06-016</t>
@@ -2506,18 +2602,24 @@
 Error appears: "Daily working hours cannot exceed 24 hours."</t>
         </is>
       </c>
-      <c r="K17" s="9" t="inlineStr"/>
-      <c r="L17" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
+      <c r="K17" s="7" t="inlineStr"/>
+      <c r="L17" s="9" t="inlineStr">
+        <is>
+          <t>System allowed entering working hours exceeding 24 hours a day (&gt; 24), allowed submitting the report, and sent email notifications without triggering validation errors.</t>
         </is>
       </c>
       <c r="M17" s="6" t="inlineStr">
         <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="N17" s="7" t="inlineStr"/>
+      <c r="O17" s="6" t="inlineStr">
+        <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N17" s="9" t="inlineStr">
+      <c r="P17" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M06-F05, Validation Rules (Section 8)</t>
         </is>
@@ -2574,18 +2676,24 @@
           <t>Non-numeric input is prevented or validation error appears: "Please enter a valid number."</t>
         </is>
       </c>
-      <c r="K18" s="4" t="inlineStr"/>
-      <c r="L18" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M18" s="10" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t>Non-numeric characters were blocked from being typed into working hours field.</t>
+        </is>
+      </c>
+      <c r="M18" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr"/>
+      <c r="O18" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="N18" s="4" t="inlineStr">
+      <c r="P18" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M06-F05, Validation Rules (Section 8)</t>
         </is>
@@ -2651,18 +2759,24 @@
 Success notification appears and page transitions to View mode.</t>
         </is>
       </c>
-      <c r="K19" s="9" t="inlineStr"/>
-      <c r="L19" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M19" s="6" t="inlineStr">
+      <c r="K19" s="7" t="inlineStr"/>
+      <c r="L19" s="9" t="inlineStr">
+        <is>
+          <t>Report was submitted successfully, status updated to Submitted, success message appeared, and form switched to View mode.</t>
+        </is>
+      </c>
+      <c r="M19" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="N19" s="7" t="inlineStr"/>
+      <c r="O19" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N19" s="9" t="inlineStr">
+      <c r="P19" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M06-F06, Business Rules 6.5</t>
         </is>
@@ -2721,18 +2835,24 @@
 Validation error message appears: "Company Supervisor Name is required."</t>
         </is>
       </c>
-      <c r="K20" s="4" t="inlineStr"/>
-      <c r="L20" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M20" s="6" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>System blocked submission and displayed validation error "Company Supervisor Name is required."</t>
+        </is>
+      </c>
+      <c r="M20" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr"/>
+      <c r="O20" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N20" s="4" t="inlineStr">
+      <c r="P20" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M06-F06, Validation Rules (Section 8)</t>
         </is>
@@ -2791,18 +2911,24 @@
 Validation error message appears: "PNV Supervisor Email is required."</t>
         </is>
       </c>
-      <c r="K21" s="9" t="inlineStr"/>
-      <c r="L21" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M21" s="6" t="inlineStr">
+      <c r="K21" s="7" t="inlineStr"/>
+      <c r="L21" s="9" t="inlineStr">
+        <is>
+          <t>System blocked submission and displayed validation error "PNV Supervisor Email is required."</t>
+        </is>
+      </c>
+      <c r="M21" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="N21" s="7" t="inlineStr"/>
+      <c r="O21" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N21" s="9" t="inlineStr">
+      <c r="P21" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M06-F06, Validation Rules (Section 8)</t>
         </is>
@@ -2861,18 +2987,24 @@
 Validation error message appears: "Invalid email address format."</t>
         </is>
       </c>
-      <c r="K22" s="4" t="inlineStr"/>
-      <c r="L22" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M22" s="6" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>System blocked submission and displayed validation error "Invalid email address format."</t>
+        </is>
+      </c>
+      <c r="M22" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr"/>
+      <c r="O22" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N22" s="4" t="inlineStr">
+      <c r="P22" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M06-F06, Validation Rules (Section 8)</t>
         </is>
@@ -2931,18 +3063,24 @@
 Validation error message appears: "Company Supervisor Email is required."</t>
         </is>
       </c>
-      <c r="K23" s="9" t="inlineStr"/>
-      <c r="L23" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M23" s="6" t="inlineStr">
+      <c r="K23" s="7" t="inlineStr"/>
+      <c r="L23" s="9" t="inlineStr">
+        <is>
+          <t>System blocked submission and displayed validation error "Company Supervisor Email is required."</t>
+        </is>
+      </c>
+      <c r="M23" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="N23" s="7" t="inlineStr"/>
+      <c r="O23" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N23" s="9" t="inlineStr">
+      <c r="P23" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M06-F06, Validation Rules (Section 8)</t>
         </is>
@@ -3001,18 +3139,24 @@
 Validation error message appears: "Invalid email address format."</t>
         </is>
       </c>
-      <c r="K24" s="4" t="inlineStr"/>
-      <c r="L24" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M24" s="6" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="4" t="inlineStr">
+        <is>
+          <t>System blocked submission and displayed validation error "Invalid email address format."</t>
+        </is>
+      </c>
+      <c r="M24" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N24" s="4" t="inlineStr">
+      <c r="P24" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M06-F06, Validation Rules (Section 8)</t>
         </is>
@@ -3071,18 +3215,24 @@
 Validation error message appears: "Challenges field is required."</t>
         </is>
       </c>
-      <c r="K25" s="9" t="inlineStr"/>
-      <c r="L25" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M25" s="6" t="inlineStr">
+      <c r="K25" s="7" t="inlineStr"/>
+      <c r="L25" s="9" t="inlineStr">
+        <is>
+          <t>System blocked submission and displayed validation error "Challenges field is required."</t>
+        </is>
+      </c>
+      <c r="M25" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="N25" s="7" t="inlineStr"/>
+      <c r="O25" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N25" s="9" t="inlineStr">
+      <c r="P25" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M06-F06, Validation Rules (Section 8)</t>
         </is>
@@ -3141,18 +3291,24 @@
 Validation error message appears: "Support Needed field is required."</t>
         </is>
       </c>
-      <c r="K26" s="4" t="inlineStr"/>
-      <c r="L26" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M26" s="6" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="4" t="inlineStr">
+        <is>
+          <t>System blocked submission and displayed validation error "Support Needed field is required."</t>
+        </is>
+      </c>
+      <c r="M26" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N26" s="4" t="inlineStr">
+      <c r="P26" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M06-F06, Validation Rules (Section 8)</t>
         </is>
@@ -3212,18 +3368,24 @@
 Report is not submitted and remains in edit form.</t>
         </is>
       </c>
-      <c r="K27" s="9" t="inlineStr"/>
-      <c r="L27" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M27" s="10" t="inlineStr">
+      <c r="K27" s="7" t="inlineStr"/>
+      <c r="L27" s="9" t="inlineStr">
+        <is>
+          <t>Confirmation popup closed upon clicking Cancel, report was not submitted, and form remained in edit mode.</t>
+        </is>
+      </c>
+      <c r="M27" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="N27" s="7" t="inlineStr"/>
+      <c r="O27" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="N27" s="9" t="inlineStr">
+      <c r="P27" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M06-F06, UI Standards</t>
         </is>
@@ -3284,18 +3446,24 @@
 Student cannot modify content.</t>
         </is>
       </c>
-      <c r="K28" s="4" t="inlineStr"/>
-      <c r="L28" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M28" s="6" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="4" t="inlineStr">
+        <is>
+          <t>Submitted report displayed in Read-Only mode with edit and save controls disabled.</t>
+        </is>
+      </c>
+      <c r="M28" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N28" s="4" t="inlineStr">
+      <c r="P28" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M06-F07, Business Rules 6.6</t>
         </is>
@@ -3354,18 +3522,24 @@
           <t>Automated email notification is delivered to both supervisor email addresses containing report summary.</t>
         </is>
       </c>
-      <c r="K29" s="9" t="inlineStr"/>
-      <c r="L29" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M29" s="6" t="inlineStr">
+      <c r="K29" s="7" t="inlineStr"/>
+      <c r="L29" s="9" t="inlineStr">
+        <is>
+          <t>Automated email notifications containing report summary were delivered to both PNV and Company supervisors upon submission.</t>
+        </is>
+      </c>
+      <c r="M29" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="N29" s="7" t="inlineStr"/>
+      <c r="O29" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N29" s="9" t="inlineStr">
+      <c r="P29" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M06-F08, Business Rules 6.7</t>
         </is>
@@ -3425,18 +3599,24 @@
 Warning message appears notifying student that email delivery failed, and error is logged.</t>
         </is>
       </c>
-      <c r="K30" s="4" t="inlineStr"/>
-      <c r="L30" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M30" s="10" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="4" t="inlineStr">
+        <is>
+          <t>Report saved successfully to database, warning notification displayed regarding email failure, and error was logged.</t>
+        </is>
+      </c>
+      <c r="M30" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="10" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="N30" s="4" t="inlineStr">
+      <c r="P30" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M06-F08, Error Handling (Section 8)</t>
         </is>
@@ -3496,18 +3676,24 @@
           <t>Staff can view complete report content (tasks, hours, challenges, supervisor info) in Read-Only mode.</t>
         </is>
       </c>
-      <c r="K31" s="9" t="inlineStr"/>
-      <c r="L31" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M31" s="6" t="inlineStr">
+      <c r="K31" s="7" t="inlineStr"/>
+      <c r="L31" s="9" t="inlineStr">
+        <is>
+          <t>Staff accessed student report list and viewed complete report content in Read-Only mode.</t>
+        </is>
+      </c>
+      <c r="M31" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="N31" s="7" t="inlineStr"/>
+      <c r="O31" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N31" s="9" t="inlineStr">
+      <c r="P31" s="9" t="inlineStr">
         <is>
           <t>Related Requirement: M06-F09, Business Rules 6.8</t>
         </is>
@@ -3567,30 +3753,36 @@
 Report content is strictly Read-Only.</t>
         </is>
       </c>
-      <c r="K32" s="4" t="inlineStr"/>
-      <c r="L32" s="5" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="M32" s="6" t="inlineStr">
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="4" t="inlineStr">
+        <is>
+          <t>Edit and delete controls were hidden for Staff role; report content remained strictly Read-Only.</t>
+        </is>
+      </c>
+      <c r="M32" s="5" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr"/>
+      <c r="O32" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N32" s="4" t="inlineStr">
+      <c r="P32" s="4" t="inlineStr">
         <is>
           <t>Related Requirement: M06-F09, Business Rules 6.8</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N32"/>
+  <autoFilter ref="A1:P32"/>
   <dataValidations count="2">
-    <dataValidation sqref="L2:L132" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Please select a valid state: Passed, Failed, or Not Run" type="list">
+    <dataValidation sqref="M2:M132" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Please select a valid state: Passed, Failed, or Not Run" type="list">
       <formula1>"Passed,Failed,Not Run"</formula1>
     </dataValidation>
-    <dataValidation sqref="M2:M132" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Priority" error="Please select a valid priority: High, Medium, or Low" type="list">
+    <dataValidation sqref="O2:O132" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Priority" error="Please select a valid priority: High, Medium, or Low" type="list">
       <formula1>"High,Medium,Low"</formula1>
     </dataValidation>
   </dataValidations>
